--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45849</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>46127</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>46002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46071</v>
+        <v>44959</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2904,13 +2904,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2919,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2937,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2950,42 +2945,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2999,10 +2994,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46092</v>
+        <v>46029</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3014,13 +3009,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3056,50 +3046,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3113,10 +3103,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46092</v>
+        <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3128,13 +3118,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3146,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3158,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3174,46 +3159,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3227,10 +3212,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46094</v>
+        <v>46071</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3242,18 +3227,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3267,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3279,50 +3269,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3336,10 +3322,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45726</v>
+        <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,11 +3337,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3388,46 +3379,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3441,10 +3436,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45133</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,7 +3457,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3498,50 +3493,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3555,10 +3550,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44959</v>
+        <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3571,10 +3566,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3583,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3595,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3607,46 +3602,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3660,10 +3659,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46029</v>
+        <v>45133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3675,8 +3674,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3716,46 +3720,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3769,10 +3773,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46043</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3785,20 +3789,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3809,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3821,43 +3825,39 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,11 +5133,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44995</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5253,7 +5253,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44757</v>
+        <v>45675</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44995</v>
+        <v>44735</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44993</v>
+        <v>45414</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5472,7 +5472,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44777</v>
+        <v>45439</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5545,7 +5545,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45849</v>
+        <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5574,13 +5574,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5623,7 +5618,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5637,10 +5632,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45854</v>
+        <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5652,13 +5647,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5701,7 +5691,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5715,10 +5705,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46072</v>
+        <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5731,7 +5721,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5774,7 +5764,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5788,10 +5778,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45869</v>
+        <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5804,7 +5794,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5847,7 +5837,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5861,10 +5851,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>46042</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5877,7 +5867,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5920,7 +5910,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5930,14 +5920,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45075</v>
+        <v>45194</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5950,7 +5940,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5993,7 +5983,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6003,14 +5993,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45931</v>
+        <v>46052</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6023,7 +6013,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6066,7 +6056,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6080,10 +6070,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45937</v>
+        <v>46052</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6096,7 +6086,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6139,7 +6129,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6149,14 +6139,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46085</v>
+        <v>45922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6169,7 +6159,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6212,7 +6202,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6226,10 +6216,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46091</v>
+        <v>45849</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6247,7 +6237,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6290,7 +6280,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6300,14 +6290,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46092</v>
+        <v>45931</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6319,13 +6309,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6368,7 +6353,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6382,10 +6367,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46092</v>
+        <v>45854</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6403,7 +6388,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6442,31 +6427,11 @@
         <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr"/>
-      <c r="Z62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6476,14 +6441,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46092</v>
+        <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6495,13 +6460,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6544,7 +6504,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6558,10 +6518,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46092</v>
+        <v>46072</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6573,13 +6533,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6622,7 +6577,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6636,10 +6591,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46092</v>
+        <v>45869</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6651,13 +6606,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6700,7 +6650,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6714,10 +6664,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44518</v>
+        <v>45937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6730,7 +6680,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6773,7 +6723,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6783,14 +6733,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45994</v>
+        <v>46085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6802,13 +6752,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6851,7 +6796,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6865,10 +6810,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46135</v>
+        <v>45642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6881,7 +6826,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6924,7 +6869,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6938,10 +6883,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44518</v>
+        <v>46091</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6953,8 +6898,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6997,7 +6947,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7011,10 +6961,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46029</v>
+        <v>46092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7026,8 +6976,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7066,11 +7021,31 @@
         <v>0</v>
       </c>
       <c r="V70" s="2" t="inlineStr"/>
+      <c r="Z70">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA70">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB70">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC70">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD70">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7084,10 +7059,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45770</v>
+        <v>46092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7099,8 +7074,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7143,7 +7123,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7157,10 +7137,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45352</v>
+        <v>46092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7178,7 +7158,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7221,7 +7201,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7235,10 +7215,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45955</v>
+        <v>46092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7250,8 +7230,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7294,7 +7279,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7308,10 +7293,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45843</v>
+        <v>46092</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7323,8 +7308,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7367,7 +7357,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7381,10 +7371,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46042</v>
+        <v>45307</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7397,7 +7387,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7440,7 +7430,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7454,10 +7444,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45112</v>
+        <v>46135</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7469,13 +7459,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7518,7 +7503,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7532,10 +7517,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46043</v>
+        <v>45955</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7548,7 +7533,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7591,7 +7576,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7605,10 +7590,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45306</v>
+        <v>45994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7626,7 +7611,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7669,7 +7654,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7683,10 +7668,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46052</v>
+        <v>45075</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7699,7 +7684,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7742,7 +7727,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7756,10 +7741,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46052</v>
+        <v>45843</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7772,7 +7757,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7832,7 +7817,7 @@
         <v>46140</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7905,7 +7890,7 @@
         <v>46135</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7961,7 +7946,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7971,14 +7956,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45194</v>
+        <v>44518</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7991,7 +7976,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8034,7 +8019,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8044,14 +8029,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44673</v>
+        <v>46167</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8064,7 +8049,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8107,7 +8092,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8121,10 +8106,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45112</v>
+        <v>44995</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8136,13 +8121,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8185,7 +8165,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8199,10 +8179,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45223</v>
+        <v>46255</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8214,8 +8194,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>16.3</v>
+        <v>7.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8258,7 +8243,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8272,10 +8257,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46167</v>
+        <v>46261</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8287,8 +8272,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8331,7 +8321,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8341,14 +8331,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45642</v>
+        <v>46193</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8361,7 +8351,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8404,7 +8394,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8418,10 +8408,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45414</v>
+        <v>46275</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8433,8 +8423,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8477,7 +8472,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8491,10 +8486,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45307</v>
+        <v>46275</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8504,6 +8499,11 @@
       <c r="G90" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -8550,7 +8550,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45675</v>
+        <v>46275</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8579,8 +8579,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8623,7 +8628,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8637,10 +8642,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44993</v>
+        <v>44757</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8653,7 +8658,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8696,7 +8701,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8710,10 +8715,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45187</v>
+        <v>44777</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8725,13 +8730,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8774,7 +8774,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8788,10 +8788,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44791</v>
+        <v>45223</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8803,13 +8803,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>16.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8852,7 +8847,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8866,10 +8861,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44735</v>
+        <v>44518</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8882,7 +8877,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8925,7 +8920,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8939,10 +8934,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46255</v>
+        <v>44846</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8954,13 +8949,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9020,7 +9010,7 @@
         <v>45675</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9093,7 +9083,7 @@
         <v>44959</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9149,7 +9139,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9163,10 +9153,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46261</v>
+        <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9178,13 +9168,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9227,7 +9212,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9241,10 +9226,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44846</v>
+        <v>45112</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9256,8 +9241,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9300,7 +9290,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9310,14 +9300,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46193</v>
+        <v>45187</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9329,8 +9319,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9373,7 +9368,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9387,10 +9382,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45034</v>
+        <v>45352</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9402,8 +9397,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46275</v>
+        <v>45770</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9475,13 +9475,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9524,7 +9519,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9538,10 +9533,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46275</v>
+        <v>45390</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9559,7 +9554,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9602,7 +9597,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9616,10 +9611,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46275</v>
+        <v>45306</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9637,7 +9632,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9680,7 +9675,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9694,10 +9689,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45300</v>
+        <v>45112</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9709,8 +9704,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45439</v>
+        <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         <v>37</v>
       </c>
       <c r="T2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12958-2026</t>
+          <t>A 17101-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46092</v>
+        <v>45034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,22 +1906,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1936,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1948,9 +1943,127 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Ullticka
+Grön sköldmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 12958-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallkötticka
 Ullticka
@@ -1959,149 +2072,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17101-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45034</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Ullticka
-Grön sköldmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
         <v/>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34859-2025</t>
+          <t>A 13004-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45849</v>
+        <v>46092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,19 +2362,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2386,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2398,371 +2398,371 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 34859-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Mörk husmossa
 Rostfläck</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 13004-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 61768-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44959</v>
+        <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2941,46 +2941,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46029</v>
+        <v>46092</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3009,8 +3009,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3046,50 +3051,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3103,10 +3108,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46043</v>
+        <v>46092</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3118,8 +3123,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3131,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3143,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3159,46 +3169,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3212,10 +3222,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46071</v>
+        <v>46094</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3227,22 +3237,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3257,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3269,46 +3274,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3322,10 +3331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46092</v>
+        <v>45726</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3337,16 +3346,11 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3379,50 +3383,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>44959</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3451,26 +3451,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3481,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3493,50 +3488,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3550,10 +3541,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46094</v>
+        <v>45133</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3565,8 +3556,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3602,50 +3598,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3659,10 +3655,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45133</v>
+        <v>46029</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3674,13 +3670,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3720,46 +3711,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3773,10 +3764,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45726</v>
+        <v>46043</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3789,10 +3780,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3801,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3813,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3825,46 +3816,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3878,10 +3873,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44497</v>
+        <v>46071</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3893,18 +3888,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3930,46 +3930,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44518</v>
+        <v>44497</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3999,19 +3999,19 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4039,35 +4039,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44548</v>
+        <v>45390</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5058,8 +5058,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5102,7 +5107,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5116,10 +5121,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44791</v>
+        <v>45414</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5131,13 +5136,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>44548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5253,7 +5253,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45675</v>
+        <v>45307</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5336,14 +5336,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44735</v>
+        <v>46085</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45414</v>
+        <v>46091</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5428,8 +5428,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5472,7 +5477,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5486,10 +5491,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45439</v>
+        <v>46092</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5501,8 +5506,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5545,7 +5555,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5559,10 +5569,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46029</v>
+        <v>46092</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5574,8 +5584,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5614,11 +5629,31 @@
         <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
+      <c r="Z51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5632,10 +5667,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44995</v>
+        <v>46092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5647,8 +5682,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5691,7 +5731,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5705,10 +5745,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44993</v>
+        <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5720,8 +5760,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5764,7 +5809,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5778,10 +5823,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46043</v>
+        <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5793,8 +5838,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5837,7 +5887,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5851,10 +5901,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46042</v>
+        <v>45675</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5867,7 +5917,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5910,7 +5960,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5920,14 +5970,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45194</v>
+        <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5940,7 +5990,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5983,7 +6033,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5993,14 +6043,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46052</v>
+        <v>45931</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6013,7 +6063,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6056,7 +6106,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6070,10 +6120,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46052</v>
+        <v>44995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6086,7 +6136,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6129,7 +6179,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6143,10 +6193,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45922</v>
+        <v>45937</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6159,7 +6209,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6202,7 +6252,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6216,10 +6266,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45849</v>
+        <v>46135</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6231,13 +6281,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6280,7 +6325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6290,14 +6335,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45931</v>
+        <v>44757</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6310,7 +6355,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6353,7 +6398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6367,10 +6412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45854</v>
+        <v>44995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6382,13 +6427,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6431,7 +6471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6441,14 +6481,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44673</v>
+        <v>44993</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6461,7 +6501,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6504,7 +6544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6518,10 +6558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46072</v>
+        <v>44993</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6534,7 +6574,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6577,7 +6617,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6591,10 +6631,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45869</v>
+        <v>44777</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6607,7 +6647,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6650,7 +6690,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6664,10 +6704,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45937</v>
+        <v>45955</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6680,7 +6720,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6723,7 +6763,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6733,14 +6773,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46085</v>
+        <v>45843</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6753,7 +6793,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6796,7 +6836,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6810,10 +6850,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45642</v>
+        <v>45075</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6826,7 +6866,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6869,7 +6909,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6883,10 +6923,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46091</v>
+        <v>45187</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6900,11 +6940,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6947,7 +6987,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6961,10 +7001,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46092</v>
+        <v>46140</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6976,13 +7016,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7021,31 +7056,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="2" t="inlineStr"/>
-      <c r="Z70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD70">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7059,10 +7074,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46092</v>
+        <v>46135</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7074,13 +7089,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7123,7 +7133,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7137,10 +7147,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46092</v>
+        <v>45994</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7158,7 +7168,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7201,7 +7211,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7215,10 +7225,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46092</v>
+        <v>44791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7232,11 +7242,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7279,7 +7289,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7293,10 +7303,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46092</v>
+        <v>44518</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7308,13 +7318,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7357,7 +7362,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7371,10 +7376,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45307</v>
+        <v>46029</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7430,7 +7435,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7444,10 +7449,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46135</v>
+        <v>46167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7460,7 +7465,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7503,7 +7508,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7517,10 +7522,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45955</v>
+        <v>46042</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7533,7 +7538,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7576,7 +7581,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7590,10 +7595,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45994</v>
+        <v>46043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7605,13 +7610,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7654,7 +7654,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45075</v>
+        <v>46052</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7727,7 +7727,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45843</v>
+        <v>46052</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7800,7 +7800,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46140</v>
+        <v>44518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7873,7 +7873,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46135</v>
+        <v>46072</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7946,7 +7946,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44518</v>
+        <v>45770</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46167</v>
+        <v>45352</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8048,8 +8048,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8092,7 +8097,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8106,10 +8111,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44995</v>
+        <v>45112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8121,8 +8126,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8165,7 +8175,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8179,10 +8189,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46255</v>
+        <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8194,13 +8204,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8243,7 +8248,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8257,10 +8262,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46261</v>
+        <v>45306</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8278,7 +8283,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8321,7 +8326,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8331,14 +8336,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46193</v>
+        <v>45675</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8351,7 +8356,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8394,7 +8399,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8408,10 +8413,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46275</v>
+        <v>44959</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8423,13 +8428,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8482,14 +8482,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46275</v>
+        <v>45194</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8501,13 +8501,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8550,7 +8545,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8564,10 +8559,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46275</v>
+        <v>46255</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8585,7 +8580,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8628,7 +8623,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8638,14 +8633,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44757</v>
+        <v>44673</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8658,7 +8653,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8701,7 +8696,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8715,10 +8710,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44777</v>
+        <v>45112</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8730,8 +8725,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8791,7 +8791,7 @@
         <v>45223</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44518</v>
+        <v>45642</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>44846</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45675</v>
+        <v>46261</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9022,8 +9022,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9066,7 +9071,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9080,10 +9085,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44959</v>
+        <v>45034</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9096,7 +9101,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9139,7 +9144,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9149,14 +9154,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44993</v>
+        <v>46193</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9169,7 +9174,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9212,7 +9217,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9226,10 +9231,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45112</v>
+        <v>46275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9247,7 +9252,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9290,7 +9295,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9304,10 +9309,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45187</v>
+        <v>46275</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9321,11 +9326,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9368,7 +9373,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9382,10 +9387,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45352</v>
+        <v>46275</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9403,7 +9408,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9446,7 +9451,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9460,10 +9465,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45770</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9476,7 +9481,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9519,7 +9524,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9533,10 +9538,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45390</v>
+        <v>45439</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9548,13 +9553,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9597,7 +9597,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45306</v>
+        <v>45849</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9675,7 +9675,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45112</v>
+        <v>45854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45300</v>
+        <v>45869</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17101-2023</t>
+          <t>A 12958-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45034</v>
+        <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1906,17 +1906,22 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1931,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1943,9 +1948,122 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallkötticka
+Ullticka
+Blodticka
+Vågbandad barkbock
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17101-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45034</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
         <v>4</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -1954,154 +2072,36 @@
 Trådticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 12958-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallkötticka
-Ullticka
-Blodticka
-Vågbandad barkbock
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
         <v/>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13004-2026</t>
+          <t>A 34859-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46092</v>
+        <v>45849</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,19 +2362,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>6.1</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2386,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2398,371 +2398,371 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mörk husmossa
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 13004-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 18576-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>4.8</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Kransmossa</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 61768-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 34859-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45849</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Mörk husmossa
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44518</v>
+        <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>8.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2929,10 +2929,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2941,46 +2941,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2994,10 +2998,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46092</v>
+        <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3009,13 +3013,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3055,46 +3054,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3108,10 +3107,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46092</v>
+        <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3125,23 +3124,23 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3156,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3165,50 +3164,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3222,10 +3217,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3237,8 +3232,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3262,10 +3262,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3278,46 +3278,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45726</v>
+        <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3346,11 +3346,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3359,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3371,10 +3376,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3383,39 +3388,43 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
@@ -3439,7 +3448,7 @@
         <v>44959</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3527,7 +3536,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3541,10 +3550,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45133</v>
+        <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3556,13 +3565,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3598,50 +3602,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3655,10 +3659,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46029</v>
+        <v>45133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3670,8 +3674,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3711,46 +3720,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3764,10 +3773,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46043</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3780,20 +3789,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3804,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3816,50 +3825,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3873,10 +3878,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46071</v>
+        <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3888,22 +3893,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3930,46 +3930,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44497</v>
+        <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3999,20 +3999,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4039,35 +4039,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45390</v>
+        <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5058,13 +5058,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5107,7 +5102,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45414</v>
+        <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5136,8 +5131,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44548</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5253,7 +5253,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45307</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5336,14 +5336,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46085</v>
+        <v>45675</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46091</v>
+        <v>45414</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5428,13 +5428,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5477,7 +5472,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5491,10 +5486,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46092</v>
+        <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5506,13 +5501,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5555,7 +5545,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5569,10 +5559,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46092</v>
+        <v>45439</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5584,13 +5574,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5629,31 +5614,11 @@
         <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
-      <c r="Z51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5667,10 +5632,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46092</v>
+        <v>46029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5682,13 +5647,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5731,7 +5691,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5745,10 +5705,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46092</v>
+        <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,13 +5720,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5809,7 +5764,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5819,14 +5774,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46092</v>
+        <v>45194</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5838,13 +5793,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5887,7 +5837,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5897,14 +5847,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45675</v>
+        <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5917,7 +5867,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5977,7 +5927,7 @@
         <v>45922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6033,7 +5983,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6043,14 +5993,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45931</v>
+        <v>45849</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6062,8 +6012,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6106,7 +6061,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6120,10 +6075,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44995</v>
+        <v>45854</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6135,8 +6090,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6179,7 +6139,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6193,10 +6153,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45937</v>
+        <v>45642</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6252,7 +6212,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6262,14 +6222,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46135</v>
+        <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6282,7 +6242,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6325,7 +6285,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6339,10 +6299,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44757</v>
+        <v>46043</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6355,7 +6315,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6398,7 +6358,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6412,10 +6372,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44995</v>
+        <v>45869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6428,7 +6388,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6471,7 +6431,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6485,10 +6445,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44993</v>
+        <v>46042</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6501,7 +6461,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6544,7 +6504,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6558,10 +6518,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44993</v>
+        <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6574,7 +6534,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6617,7 +6577,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6631,10 +6591,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44777</v>
+        <v>46052</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6647,7 +6607,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6690,7 +6650,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6704,10 +6664,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45955</v>
+        <v>46052</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6720,7 +6680,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6763,7 +6723,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6777,10 +6737,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45843</v>
+        <v>45307</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6793,7 +6753,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6836,7 +6796,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6850,10 +6810,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45075</v>
+        <v>46072</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6866,7 +6826,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6909,7 +6869,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6923,10 +6883,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45187</v>
+        <v>45994</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6940,11 +6900,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6987,7 +6947,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6997,14 +6957,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46140</v>
+        <v>46085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7017,7 +6977,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7060,7 +7020,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7074,10 +7034,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46135</v>
+        <v>45075</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7090,7 +7050,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7133,7 +7093,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7147,10 +7107,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45994</v>
+        <v>46091</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7168,7 +7128,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7211,7 +7171,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7225,10 +7185,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44791</v>
+        <v>46092</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7242,11 +7202,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7285,11 +7245,31 @@
         <v>0</v>
       </c>
       <c r="V73" s="2" t="inlineStr"/>
+      <c r="Z73">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA73">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB73">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC73">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD73">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7303,10 +7283,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7318,8 +7298,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7362,7 +7347,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7376,10 +7361,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46029</v>
+        <v>46092</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7391,8 +7376,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7435,7 +7425,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7449,10 +7439,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46167</v>
+        <v>46092</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7464,8 +7454,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7508,7 +7503,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7522,10 +7517,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46042</v>
+        <v>46092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7537,8 +7532,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46043</v>
+        <v>44518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7654,7 +7654,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46052</v>
+        <v>46135</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7727,7 +7727,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46052</v>
+        <v>44995</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7800,7 +7800,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44518</v>
+        <v>45955</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7873,7 +7873,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46072</v>
+        <v>45843</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7946,7 +7946,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45770</v>
+        <v>46140</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45352</v>
+        <v>46135</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8048,13 +8048,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8097,7 +8092,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8111,10 +8106,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45112</v>
+        <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8126,13 +8121,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8175,7 +8165,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8189,10 +8179,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44735</v>
+        <v>44777</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8205,7 +8195,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8248,7 +8238,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8262,10 +8252,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45306</v>
+        <v>45223</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8277,13 +8267,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>3.6</v>
+        <v>16.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8326,7 +8311,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8340,10 +8325,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45675</v>
+        <v>44518</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8356,7 +8341,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8399,7 +8384,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8413,10 +8398,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44959</v>
+        <v>46167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8429,7 +8414,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8472,7 +8457,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8482,14 +8467,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45194</v>
+        <v>44846</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8502,7 +8487,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8545,7 +8530,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8559,10 +8544,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46255</v>
+        <v>45675</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8574,13 +8559,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8623,7 +8603,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8633,14 +8613,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44673</v>
+        <v>44959</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8653,7 +8633,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8696,7 +8676,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8710,10 +8690,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45112</v>
+        <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8725,13 +8705,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8774,7 +8749,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8788,10 +8763,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45223</v>
+        <v>45112</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8803,8 +8778,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>16.3</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8847,7 +8827,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8861,10 +8841,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45642</v>
+        <v>45187</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8876,8 +8856,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8920,7 +8905,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8934,10 +8919,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44846</v>
+        <v>45352</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8949,8 +8934,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8993,7 +8983,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9007,10 +8997,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46261</v>
+        <v>46255</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9028,7 +9018,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9071,7 +9061,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9085,10 +9075,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45034</v>
+        <v>45770</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9101,7 +9091,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9144,7 +9134,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9154,14 +9144,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46193</v>
+        <v>46261</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9171,6 +9161,11 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -9217,7 +9212,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9231,10 +9226,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46275</v>
+        <v>45390</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9252,7 +9247,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9295,7 +9290,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9305,14 +9300,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46275</v>
+        <v>46193</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9324,13 +9319,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9390,7 +9380,7 @@
         <v>46275</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9451,7 +9441,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9465,10 +9455,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9480,8 +9470,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9524,7 +9519,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9538,10 +9533,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45439</v>
+        <v>46275</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9553,8 +9548,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9597,7 +9597,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45849</v>
+        <v>46275</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9675,7 +9675,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9689,10 +9689,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45854</v>
+        <v>45112</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45869</v>
+        <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34859-2025</t>
+          <t>A 13004-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45849</v>
+        <v>46092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2362,19 +2362,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2386,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2398,371 +2398,371 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 34859-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Mörk husmossa
 Rostfläck</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 61768-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>46002</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>3</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Kamjordstjärna</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 13004-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46029</v>
+        <v>46071</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2904,18 +2904,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2929,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2945,46 +2950,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2998,10 +2999,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46043</v>
+        <v>46092</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3013,8 +3014,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3054,46 +3060,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3107,10 +3113,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3124,23 +3130,23 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3155,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3164,46 +3170,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3217,10 +3227,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3232,13 +3242,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3250,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3262,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3278,46 +3283,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3331,10 +3336,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46092</v>
+        <v>45726</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3346,26 +3351,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3376,10 +3376,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3388,50 +3388,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3445,10 +3441,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44959</v>
+        <v>45133</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3460,11 +3456,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3473,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3485,10 +3486,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3501,42 +3502,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3550,10 +3555,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46094</v>
+        <v>44497</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3566,13 +3571,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3606,46 +3611,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3659,10 +3660,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45133</v>
+        <v>44518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3674,26 +3675,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3704,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3716,50 +3712,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3773,10 +3765,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45726</v>
+        <v>44959</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3789,7 +3781,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3829,42 +3821,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3878,10 +3870,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44497</v>
+        <v>46029</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3894,13 +3886,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3930,46 +3922,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3983,10 +3979,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44518</v>
+        <v>46043</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3999,10 +3995,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -4011,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4023,10 +4019,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4039,35 +4035,39 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44791</v>
+        <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,11 +5133,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>46072</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5253,7 +5253,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>44995</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5336,14 +5336,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45675</v>
+        <v>46085</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45414</v>
+        <v>44757</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5472,7 +5472,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5489,7 +5489,7 @@
         <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5545,7 +5545,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45439</v>
+        <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46029</v>
+        <v>46091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5647,8 +5647,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5691,7 +5696,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5705,10 +5710,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44993</v>
+        <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5720,8 +5725,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5764,7 +5774,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5774,14 +5784,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45194</v>
+        <v>44777</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5837,7 +5847,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5847,14 +5857,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44673</v>
+        <v>46092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5864,6 +5874,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5906,11 +5921,31 @@
         <v>0</v>
       </c>
       <c r="V55" s="2" t="inlineStr"/>
+      <c r="Z55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD55">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5924,10 +5959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45922</v>
+        <v>46092</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5939,8 +5974,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5983,7 +6023,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5997,10 +6037,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45849</v>
+        <v>46092</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6018,7 +6058,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6061,7 +6101,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6075,10 +6115,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45854</v>
+        <v>46092</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6096,7 +6136,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6139,7 +6179,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6153,10 +6193,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45642</v>
+        <v>45849</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6168,8 +6208,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6212,7 +6257,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6222,14 +6267,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45931</v>
+        <v>45854</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6241,8 +6286,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6285,7 +6335,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6299,10 +6349,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46043</v>
+        <v>45075</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6315,7 +6365,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6375,7 +6425,7 @@
         <v>45869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6431,7 +6481,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6445,10 +6495,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46042</v>
+        <v>46135</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6461,7 +6511,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6504,7 +6554,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6518,10 +6568,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45937</v>
+        <v>45922</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6534,7 +6584,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6577,7 +6627,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6591,10 +6641,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46052</v>
+        <v>45955</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6607,7 +6657,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6650,7 +6700,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6664,10 +6714,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46052</v>
+        <v>44518</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6680,7 +6730,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6723,7 +6773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6737,10 +6787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45307</v>
+        <v>45843</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6753,7 +6803,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6796,7 +6846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6810,10 +6860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46072</v>
+        <v>46140</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6826,7 +6876,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6869,7 +6919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6883,10 +6933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45994</v>
+        <v>46135</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6898,13 +6948,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6947,7 +6992,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6961,10 +7006,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46085</v>
+        <v>45931</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6977,7 +7022,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7020,7 +7065,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7034,10 +7079,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45075</v>
+        <v>44518</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7050,7 +7095,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7093,7 +7138,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7107,10 +7152,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46091</v>
+        <v>45937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7122,13 +7167,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7171,7 +7211,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7185,10 +7225,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46092</v>
+        <v>45770</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7200,13 +7240,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7245,31 +7280,11 @@
         <v>0</v>
       </c>
       <c r="V73" s="2" t="inlineStr"/>
-      <c r="Z73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD73">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7283,10 +7298,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46092</v>
+        <v>45352</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7304,7 +7319,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7347,7 +7362,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7361,10 +7376,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46092</v>
+        <v>45112</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7382,7 +7397,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7425,7 +7440,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7439,10 +7454,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46092</v>
+        <v>46167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7454,13 +7469,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7503,7 +7513,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7517,10 +7527,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46092</v>
+        <v>45306</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7538,7 +7548,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7581,7 +7591,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7591,14 +7601,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44518</v>
+        <v>45194</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7611,7 +7621,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.9</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7654,7 +7664,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7664,14 +7674,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46135</v>
+        <v>44673</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7684,7 +7694,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7727,7 +7737,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7741,10 +7751,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44995</v>
+        <v>45112</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7756,8 +7766,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7800,7 +7815,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7814,10 +7829,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45955</v>
+        <v>45223</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7830,7 +7845,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>16.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7873,7 +7888,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7887,10 +7902,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45843</v>
+        <v>45642</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7903,7 +7918,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7946,7 +7961,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7960,10 +7975,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46140</v>
+        <v>45414</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7976,7 +7991,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8019,7 +8034,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8033,10 +8048,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46135</v>
+        <v>45307</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8049,7 +8064,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8092,7 +8107,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8106,10 +8121,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44757</v>
+        <v>45994</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8121,8 +8136,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8165,7 +8185,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8179,10 +8199,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44777</v>
+        <v>46255</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8194,8 +8214,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8238,7 +8263,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8252,10 +8277,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45223</v>
+        <v>46261</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8267,8 +8292,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>16.3</v>
+        <v>7.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8311,7 +8341,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8325,10 +8355,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44518</v>
+        <v>45675</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8341,7 +8371,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8384,7 +8414,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8394,14 +8424,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46167</v>
+        <v>46193</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8414,7 +8444,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8457,7 +8487,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8471,10 +8501,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44846</v>
+        <v>46275</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8486,8 +8516,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8530,7 +8565,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8544,10 +8579,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45675</v>
+        <v>46275</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8559,8 +8594,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8603,7 +8643,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8617,10 +8657,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44959</v>
+        <v>46275</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8632,8 +8672,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8693,7 +8738,7 @@
         <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8749,7 +8794,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8763,10 +8808,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45112</v>
+        <v>45187</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8780,11 +8825,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8827,7 +8872,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8841,10 +8886,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45187</v>
+        <v>46029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8856,13 +8901,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8905,7 +8945,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8919,10 +8959,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45352</v>
+        <v>44791</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8936,11 +8976,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8983,7 +9023,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8997,10 +9037,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46255</v>
+        <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9012,13 +9052,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9061,7 +9096,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9075,10 +9110,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45770</v>
+        <v>46043</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9091,7 +9126,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9134,7 +9169,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9148,10 +9183,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46261</v>
+        <v>44735</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9163,13 +9198,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9212,7 +9242,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9226,10 +9256,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45390</v>
+        <v>46052</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9241,13 +9271,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9290,7 +9315,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9300,14 +9325,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46193</v>
+        <v>46052</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9320,7 +9345,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9363,7 +9388,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9377,10 +9402,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46275</v>
+        <v>45675</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9392,13 +9417,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9441,7 +9461,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9455,10 +9475,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45306</v>
+        <v>44959</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9470,13 +9490,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9519,7 +9534,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9533,10 +9548,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46275</v>
+        <v>44846</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9548,13 +9563,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9597,7 +9607,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9611,10 +9621,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46275</v>
+        <v>45034</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9626,13 +9636,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9675,7 +9680,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9689,10 +9694,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45112</v>
+        <v>45300</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9704,13 +9709,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45300</v>
+        <v>45439</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13004-2026</t>
+          <t>A 61768-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46092</v>
+        <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,25 +2356,20 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2389,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2398,371 +2393,376 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 13004-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 34859-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45849</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I19" t="n">
         <v>6.1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Mörk husmossa
 Rostfläck</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 61768-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46071</v>
+        <v>45133</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2906,20 +2906,20 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2950,42 +2950,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2999,10 +3003,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46092</v>
+        <v>44959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3014,26 +3018,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -3044,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3056,50 +3055,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46092</v>
+        <v>46029</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3128,13 +3123,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3146,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3158,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3170,50 +3160,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3227,10 +3217,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46094</v>
+        <v>46043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3243,7 +3233,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3287,42 +3277,42 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3336,10 +3326,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45726</v>
+        <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3351,8 +3341,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3361,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3379,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3392,42 +3387,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3441,10 +3436,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45133</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,7 +3457,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3474,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3486,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3498,50 +3493,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3555,10 +3550,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44497</v>
+        <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3570,14 +3565,19 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3611,42 +3611,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3660,10 +3664,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44518</v>
+        <v>45726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,7 +3680,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3712,46 +3716,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3765,10 +3769,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44959</v>
+        <v>46094</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3781,10 +3785,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3793,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3805,10 +3809,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3817,46 +3821,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3870,10 +3878,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46029</v>
+        <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3886,13 +3894,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3922,50 +3930,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3979,10 +3983,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46043</v>
+        <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3995,20 +3999,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -4019,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4035,39 +4039,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,11 +5133,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46072</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5253,7 +5253,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44995</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5336,14 +5336,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46085</v>
+        <v>45414</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44757</v>
+        <v>45675</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5472,7 +5472,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5489,7 +5489,7 @@
         <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5562,7 +5562,7 @@
         <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46091</v>
+        <v>45194</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5647,13 +5647,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5696,7 +5691,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5706,14 +5701,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46092</v>
+        <v>44673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5725,13 +5720,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5774,7 +5764,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5788,10 +5778,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44777</v>
+        <v>45642</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5804,7 +5794,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5847,7 +5837,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5861,10 +5851,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46092</v>
+        <v>45307</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5876,13 +5866,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5921,31 +5906,11 @@
         <v>0</v>
       </c>
       <c r="V55" s="2" t="inlineStr"/>
-      <c r="Z55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5959,10 +5924,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46092</v>
+        <v>45955</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5974,13 +5939,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6023,7 +5983,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6037,10 +5997,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46092</v>
+        <v>45075</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,13 +6012,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6101,7 +6056,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6115,10 +6070,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46092</v>
+        <v>45843</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6130,13 +6085,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6179,7 +6129,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6193,10 +6143,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45849</v>
+        <v>46140</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6208,13 +6158,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6257,7 +6202,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6271,10 +6216,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45854</v>
+        <v>46135</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6286,13 +6231,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6335,7 +6275,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6349,10 +6289,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45075</v>
+        <v>45922</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6365,7 +6305,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6408,7 +6348,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6422,10 +6362,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45869</v>
+        <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6438,7 +6378,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6481,7 +6421,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6491,14 +6431,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46135</v>
+        <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6511,7 +6451,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6554,7 +6494,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6568,10 +6508,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45922</v>
+        <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6584,7 +6524,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6627,7 +6567,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6641,10 +6581,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45955</v>
+        <v>44995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6700,7 +6640,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6714,10 +6654,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44518</v>
+        <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6729,8 +6669,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6773,7 +6718,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6787,10 +6732,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45843</v>
+        <v>46167</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6803,7 +6748,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6846,7 +6791,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6860,10 +6805,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46140</v>
+        <v>44757</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6919,7 +6864,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6933,10 +6878,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46135</v>
+        <v>44777</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6949,7 +6894,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6992,7 +6937,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7002,14 +6947,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45931</v>
+        <v>45223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7022,7 +6967,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>16.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7065,7 +7010,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7079,10 +7024,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44518</v>
+        <v>46029</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7095,7 +7040,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7138,7 +7083,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7152,10 +7097,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45937</v>
+        <v>44518</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7168,7 +7113,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7211,7 +7156,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7225,10 +7170,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45770</v>
+        <v>46043</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7241,7 +7186,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7284,7 +7229,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7298,10 +7243,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45352</v>
+        <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7313,13 +7258,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7362,7 +7302,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7376,10 +7316,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45112</v>
+        <v>44846</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7391,13 +7331,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7440,7 +7375,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7454,10 +7389,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46167</v>
+        <v>46052</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7470,7 +7405,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7513,7 +7448,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7527,10 +7462,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45306</v>
+        <v>46052</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7542,13 +7477,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7591,7 +7521,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7601,14 +7531,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45194</v>
+        <v>45675</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7621,7 +7551,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7664,7 +7594,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7674,14 +7604,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44673</v>
+        <v>44959</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7694,7 +7624,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7737,7 +7667,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7751,10 +7681,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45112</v>
+        <v>46072</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7766,13 +7696,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7815,7 +7740,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7825,14 +7750,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45223</v>
+        <v>46085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7845,7 +7770,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>16.3</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7888,7 +7813,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7902,10 +7827,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45642</v>
+        <v>44993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7918,7 +7843,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7961,7 +7886,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7975,10 +7900,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45414</v>
+        <v>45112</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7990,8 +7915,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8034,7 +7964,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8048,10 +7978,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45307</v>
+        <v>46091</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8063,8 +7993,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8107,7 +8042,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8121,10 +8056,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45994</v>
+        <v>46092</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8142,7 +8077,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8181,11 +8116,31 @@
         <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr"/>
+      <c r="Z85">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA85">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB85">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC85">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD85">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8199,10 +8154,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46255</v>
+        <v>46092</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8220,7 +8175,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8263,7 +8218,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8277,10 +8232,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46261</v>
+        <v>46092</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8298,7 +8253,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8341,7 +8296,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8355,10 +8310,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45675</v>
+        <v>46092</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8370,8 +8325,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8414,7 +8374,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8424,14 +8384,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46193</v>
+        <v>46092</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8443,8 +8403,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8487,7 +8452,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8501,10 +8466,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46275</v>
+        <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8518,11 +8483,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8565,7 +8530,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8579,10 +8544,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46275</v>
+        <v>45352</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8600,7 +8565,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8643,7 +8608,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8657,10 +8622,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46275</v>
+        <v>46135</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8672,13 +8637,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8721,7 +8681,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8735,10 +8695,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44993</v>
+        <v>45770</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8751,7 +8711,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8794,7 +8754,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8808,10 +8768,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45187</v>
+        <v>46255</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8825,11 +8785,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8872,7 +8832,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8886,10 +8846,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46029</v>
+        <v>45390</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8901,8 +8861,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8945,7 +8910,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8959,10 +8924,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44791</v>
+        <v>46261</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8976,11 +8941,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9023,7 +8988,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9037,10 +9002,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46042</v>
+        <v>45306</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9052,8 +9017,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9096,7 +9066,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9110,10 +9080,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46043</v>
+        <v>45112</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9125,8 +9095,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9169,7 +9144,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9179,14 +9154,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44735</v>
+        <v>46193</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9199,7 +9174,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9242,7 +9217,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9256,10 +9231,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46052</v>
+        <v>46275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9271,8 +9246,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9315,7 +9295,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9329,10 +9309,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46052</v>
+        <v>46275</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9344,8 +9324,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9388,7 +9373,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9402,10 +9387,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45675</v>
+        <v>46275</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9417,8 +9402,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9461,7 +9451,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9475,10 +9465,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44959</v>
+        <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9491,7 +9481,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9534,7 +9524,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9548,10 +9538,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44846</v>
+        <v>45439</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9564,7 +9554,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9607,7 +9597,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9621,10 +9611,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45034</v>
+        <v>45849</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9636,8 +9626,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9680,7 +9675,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9694,10 +9689,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45300</v>
+        <v>45854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9709,8 +9704,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9753,7 +9753,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45439</v>
+        <v>45869</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>46127</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45133</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44959</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>46029</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>46043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>45726</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>46094</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45414</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45675</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45194</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45642</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45307</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>45955</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>45075</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>45843</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>46140</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>46135</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>45922</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>45937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>46167</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44757</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44777</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>45223</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>46029</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44518</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>46043</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>46042</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44846</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>46052</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>46052</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45675</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44959</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>46072</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>46085</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>45112</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>46091</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46092</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>46092</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>46092</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>46092</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>46092</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45187</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45352</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>46135</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45770</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>46255</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45390</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>46261</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45306</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45112</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>46193</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>46275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>46275</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>46275</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>45439</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45849</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45869</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,10 +620,10 @@
         <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
@@ -638,19 +638,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
         <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T2" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="U2" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -673,12 +673,14 @@
 Skarp dropptaggsvamp
 Svartöra
 Såpfingersvamp
+Tallkötticka
 Tallticka
 Ullticka
 Blodticka
 Blomkålssvamp
 Blåmossa
 Brandticka
+Bronshjon
 Grovticka
 Gullgröppa
 Mindre märgborre
@@ -750,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1286,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1415,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1539,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1775,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1894,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2012,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2125,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2344,7 +2346,7 @@
         <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2450,7 +2452,7 @@
         <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2569,7 +2571,7 @@
         <v>46127</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2675,7 +2677,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2786,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2875,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2889,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45133</v>
+        <v>44959</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2904,26 +2906,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2934,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2950,46 +2947,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3003,10 +2996,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44959</v>
+        <v>46029</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3019,10 +3012,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -3031,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3043,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3059,42 +3052,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3108,10 +3105,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3124,7 +3121,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3160,50 +3157,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3217,10 +3214,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46043</v>
+        <v>45133</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3232,8 +3229,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3269,43 +3271,43 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3331,7 @@
         <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3441,7 @@
         <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3553,7 +3555,7 @@
         <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3652,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3664,10 +3666,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45726</v>
+        <v>46094</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3680,10 +3682,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3692,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3704,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3716,46 +3718,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3769,10 +3775,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46094</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3785,20 +3791,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3809,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3821,43 +3827,39 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
@@ -3881,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4201,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4457,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4603,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4676,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4900,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4973,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5046,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5119,7 +5121,7 @@
         <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5197,7 +5199,7 @@
         <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5270,7 +5272,7 @@
         <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5326,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5340,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45414</v>
+        <v>45675</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5356,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5399,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5413,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45675</v>
+        <v>45414</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5429,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5489,7 +5491,7 @@
         <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5545,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5555,14 +5557,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44993</v>
+        <v>45194</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5575,7 +5577,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5618,7 +5620,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5632,10 +5634,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45194</v>
+        <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5648,7 +5650,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5691,7 +5693,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5701,14 +5703,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44673</v>
+        <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5721,7 +5723,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5781,7 +5783,7 @@
         <v>45642</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5854,7 +5856,7 @@
         <v>45307</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5927,7 +5929,7 @@
         <v>45955</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5983,7 +5985,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5997,10 +5999,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45075</v>
+        <v>45843</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6013,7 +6015,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6056,7 +6058,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6070,10 +6072,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45843</v>
+        <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6086,7 +6088,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6146,7 +6148,7 @@
         <v>46140</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6202,7 +6204,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6212,14 +6214,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46135</v>
+        <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6232,7 +6234,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6275,7 +6277,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6289,10 +6291,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45922</v>
+        <v>45075</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6305,7 +6307,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6348,7 +6350,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6362,10 +6364,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44518</v>
+        <v>46135</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6378,7 +6380,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6421,7 +6423,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6431,14 +6433,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6451,7 +6453,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6494,7 +6496,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6508,10 +6510,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45937</v>
+        <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6524,7 +6526,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6567,7 +6569,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6581,10 +6583,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44995</v>
+        <v>46167</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6657,7 +6659,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6718,7 +6720,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,10 +6734,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46167</v>
+        <v>44995</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6791,7 +6793,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6805,10 +6807,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44757</v>
+        <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6821,7 +6823,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6864,7 +6866,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6878,10 +6880,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44777</v>
+        <v>46043</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6894,7 +6896,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6937,7 +6939,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6951,10 +6953,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45223</v>
+        <v>46042</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6967,7 +6969,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>16.3</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7010,7 +7012,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7024,10 +7026,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46029</v>
+        <v>46052</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7040,7 +7042,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7083,7 +7085,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7097,10 +7099,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44518</v>
+        <v>46052</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7113,7 +7115,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7156,7 +7158,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7170,10 +7172,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46043</v>
+        <v>44757</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7186,7 +7188,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7229,7 +7231,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7243,10 +7245,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46042</v>
+        <v>46072</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7259,7 +7261,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7302,7 +7304,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7316,10 +7318,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44846</v>
+        <v>44777</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7332,7 +7334,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7375,7 +7377,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7385,14 +7387,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46052</v>
+        <v>46085</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7405,7 +7407,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7448,7 +7450,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7462,10 +7464,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46052</v>
+        <v>45223</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7478,7 +7480,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>16.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7521,7 +7523,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7535,10 +7537,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45675</v>
+        <v>46091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7550,8 +7552,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7594,7 +7601,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7608,10 +7615,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44959</v>
+        <v>46092</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7623,8 +7630,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7663,11 +7675,31 @@
         <v>0</v>
       </c>
       <c r="V79" s="2" t="inlineStr"/>
+      <c r="Z79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7681,10 +7713,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46072</v>
+        <v>46092</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7696,8 +7728,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7740,7 +7777,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7750,14 +7787,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7769,8 +7806,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7813,7 +7855,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7827,10 +7869,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44993</v>
+        <v>46092</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7842,8 +7884,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7886,7 +7933,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7900,10 +7947,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45112</v>
+        <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7921,7 +7968,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7964,7 +8011,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7978,10 +8025,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46091</v>
+        <v>44518</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7993,13 +8040,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8042,7 +8084,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8056,10 +8098,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46092</v>
+        <v>44846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8071,13 +8113,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8116,31 +8153,11 @@
         <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr"/>
-      <c r="Z85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD85">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8154,10 +8171,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46092</v>
+        <v>45675</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8169,13 +8186,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8218,7 +8230,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8232,10 +8244,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46092</v>
+        <v>44959</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8247,13 +8259,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8296,7 +8303,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8310,10 +8317,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46092</v>
+        <v>46135</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8325,13 +8332,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8374,7 +8376,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8388,10 +8390,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46092</v>
+        <v>44993</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8403,13 +8405,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8452,7 +8449,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8466,10 +8463,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45187</v>
+        <v>45112</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8483,11 +8480,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8530,7 +8527,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8544,10 +8541,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45352</v>
+        <v>46255</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8565,7 +8562,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8608,7 +8605,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8622,10 +8619,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46135</v>
+        <v>46261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8637,8 +8634,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8681,7 +8683,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8695,10 +8697,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45770</v>
+        <v>45187</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8710,8 +8712,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8754,7 +8761,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8768,10 +8775,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46255</v>
+        <v>45352</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8789,7 +8796,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8832,7 +8839,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8842,14 +8849,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45390</v>
+        <v>46193</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8861,13 +8868,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8910,7 +8912,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8924,10 +8926,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8945,7 +8947,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8988,7 +8990,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9002,10 +9004,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45306</v>
+        <v>45770</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9017,13 +9019,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9066,7 +9063,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9080,10 +9077,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45112</v>
+        <v>46275</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9101,7 +9098,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9144,7 +9141,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9154,14 +9151,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46193</v>
+        <v>46275</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9173,8 +9170,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9217,7 +9219,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9231,10 +9233,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46275</v>
+        <v>45390</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9252,7 +9254,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9295,7 +9297,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9309,10 +9311,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46275</v>
+        <v>45306</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9330,7 +9332,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9373,7 +9375,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9387,10 +9389,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46275</v>
+        <v>45112</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9408,7 +9410,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9468,7 +9470,7 @@
         <v>45300</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9541,7 +9543,7 @@
         <v>45439</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9614,7 +9616,7 @@
         <v>45849</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9692,7 +9694,7 @@
         <v>45854</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9770,7 +9772,7 @@
         <v>45869</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9843,7 +9845,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12958-2026</t>
+          <t>A 17101-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46092</v>
+        <v>45034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1908,22 +1908,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1938,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1950,9 +1945,127 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Ullticka
+Grön sköldmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 12958-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallkötticka
 Ullticka
@@ -1961,149 +2074,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17101-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45034</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Ullticka
-Grön sköldmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
         <v/>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18576-2026</t>
+          <t>A 34859-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46127</v>
+        <v>45849</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,14 +2583,19 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2617,154 +2622,149 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Mörk husmossa
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>7</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Kransmossa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 34859-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45849</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Mörk husmossa
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44959</v>
+        <v>45726</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2947,42 +2947,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46029</v>
+        <v>45133</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3011,8 +3011,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3052,46 +3057,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46043</v>
+        <v>44497</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3121,13 +3126,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3161,46 +3166,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3214,10 +3215,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45133</v>
+        <v>46029</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3229,13 +3230,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3275,46 +3271,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3328,10 +3324,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46071</v>
+        <v>46043</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3343,22 +3339,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3373,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3385,46 +3376,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>44518</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,16 +3448,11 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3499,46 +3489,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3552,10 +3538,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46092</v>
+        <v>44959</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3567,26 +3553,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3597,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3609,50 +3590,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3666,10 +3643,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46094</v>
+        <v>46071</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3681,18 +3658,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3706,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3718,50 +3700,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3775,10 +3753,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45726</v>
+        <v>46092</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,11 +3768,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3803,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3815,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3827,46 +3810,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3880,10 +3867,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44497</v>
+        <v>46092</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3895,21 +3882,26 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
@@ -3920,10 +3912,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3936,42 +3928,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3985,10 +3981,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44518</v>
+        <v>46094</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4001,10 +3997,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -4013,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4025,10 +4021,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4041,35 +4037,39 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62441-2021</t>
+          <t>A 72966-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44503</v>
+        <v>44548</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 72966-2021</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 62441-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44548</v>
+        <v>44503</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44791</v>
+        <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,13 +5133,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5177,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5191,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>45390</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5211,8 +5206,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>44518</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>6.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45675</v>
+        <v>45770</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45414</v>
+        <v>45352</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5430,8 +5430,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5479,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5488,10 +5493,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44995</v>
+        <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5503,8 +5508,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5557,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5557,14 +5567,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45194</v>
+        <v>45306</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5576,8 +5586,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5620,7 +5635,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5630,14 +5645,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44673</v>
+        <v>45439</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5650,7 +5665,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5693,7 +5708,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5707,10 +5722,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44993</v>
+        <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5723,7 +5738,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5766,7 +5781,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5776,14 +5791,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45642</v>
+        <v>45931</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5796,7 +5811,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5839,7 +5854,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5853,10 +5868,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45307</v>
+        <v>45937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5869,7 +5884,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5912,7 +5927,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5926,10 +5941,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45955</v>
+        <v>44995</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5942,7 +5957,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5985,7 +6000,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5999,10 +6014,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45843</v>
+        <v>44757</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6015,7 +6030,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6058,7 +6073,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6072,10 +6087,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45922</v>
+        <v>44995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6088,7 +6103,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6131,7 +6146,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6141,14 +6156,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46140</v>
+        <v>45194</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6161,7 +6176,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6204,7 +6219,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6214,14 +6229,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45931</v>
+        <v>44993</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6234,7 +6249,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6277,7 +6292,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6291,10 +6306,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45075</v>
+        <v>44777</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6307,7 +6322,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6350,7 +6365,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6360,14 +6375,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46135</v>
+        <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6423,7 +6438,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6437,10 +6452,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45937</v>
+        <v>45112</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6452,8 +6467,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6496,7 +6516,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6510,10 +6530,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44518</v>
+        <v>45223</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6526,7 +6546,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.9</v>
+        <v>16.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6569,7 +6589,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6583,10 +6603,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46167</v>
+        <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6599,7 +6619,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6642,7 +6662,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6656,10 +6676,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45994</v>
+        <v>45075</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6671,13 +6691,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6720,7 +6735,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6734,10 +6749,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44995</v>
+        <v>45414</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6765,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6793,7 +6808,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6807,10 +6822,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46029</v>
+        <v>45994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6822,8 +6837,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6866,7 +6886,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6880,10 +6900,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46043</v>
+        <v>45307</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6896,7 +6916,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6939,7 +6959,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6953,10 +6973,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6969,7 +6989,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7012,7 +7032,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7026,10 +7046,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46052</v>
+        <v>46042</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7042,7 +7062,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7085,7 +7105,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7099,10 +7119,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46052</v>
+        <v>46043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7115,7 +7135,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7158,7 +7178,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7172,10 +7192,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44757</v>
+        <v>46052</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7188,7 +7208,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7231,7 +7251,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7245,10 +7265,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7261,7 +7281,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7304,7 +7324,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7318,10 +7338,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44777</v>
+        <v>45675</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7334,7 +7354,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7377,7 +7397,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7387,14 +7407,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46085</v>
+        <v>46072</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7407,7 +7427,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7450,7 +7470,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7464,10 +7484,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45223</v>
+        <v>44993</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7480,7 +7500,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>16.3</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7523,7 +7543,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7537,10 +7557,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46091</v>
+        <v>45187</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7554,11 +7574,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7601,7 +7621,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7611,14 +7631,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7630,13 +7650,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7675,31 +7690,11 @@
         <v>0</v>
       </c>
       <c r="V79" s="2" t="inlineStr"/>
-      <c r="Z79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7713,10 +7708,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7734,7 +7729,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7777,7 +7772,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7794,7 +7789,7 @@
         <v>46092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7812,7 +7807,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7855,7 +7850,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7872,7 +7867,7 @@
         <v>46092</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7890,7 +7885,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7929,6 +7924,26 @@
         <v>0</v>
       </c>
       <c r="V82" s="2" t="inlineStr"/>
+      <c r="Z82">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA82">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB82">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC82">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD82">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
@@ -7950,7 +7965,7 @@
         <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8011,7 +8026,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8025,10 +8040,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8040,8 +8055,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8084,7 +8104,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8098,10 +8118,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44846</v>
+        <v>46092</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8113,8 +8133,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8157,7 +8182,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8171,10 +8196,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45675</v>
+        <v>44791</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8186,8 +8211,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8230,7 +8260,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8244,10 +8274,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44959</v>
+        <v>45849</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8259,8 +8289,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8303,7 +8338,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8317,10 +8352,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46135</v>
+        <v>45854</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8332,8 +8367,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8376,7 +8416,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8390,10 +8430,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44993</v>
+        <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8406,7 +8446,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8449,7 +8489,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8463,10 +8503,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45112</v>
+        <v>45869</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8478,13 +8518,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8527,7 +8562,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8541,10 +8576,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46255</v>
+        <v>45675</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8556,13 +8591,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8605,7 +8635,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8619,10 +8649,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46261</v>
+        <v>44959</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8634,13 +8664,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8683,7 +8708,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8697,10 +8722,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45187</v>
+        <v>46135</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8712,13 +8737,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8761,7 +8781,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8775,10 +8795,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45352</v>
+        <v>44846</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8790,13 +8810,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8839,7 +8854,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8849,14 +8864,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46193</v>
+        <v>45955</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8869,7 +8884,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8912,7 +8927,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8926,10 +8941,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46275</v>
+        <v>45843</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8941,13 +8956,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8990,7 +9000,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9004,10 +9014,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45770</v>
+        <v>45034</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9020,7 +9030,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9063,7 +9073,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9077,10 +9087,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46275</v>
+        <v>46140</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9092,13 +9102,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9141,7 +9146,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9155,10 +9160,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46275</v>
+        <v>46135</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9170,13 +9175,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9219,7 +9219,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45390</v>
+        <v>45300</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9248,13 +9248,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9297,7 +9292,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9311,10 +9306,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45306</v>
+        <v>46167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9326,13 +9321,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9375,7 +9365,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9389,10 +9379,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45112</v>
+        <v>46255</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9410,7 +9400,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9453,7 +9443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9467,10 +9457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45300</v>
+        <v>46261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9482,8 +9472,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9526,7 +9521,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9536,14 +9531,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45439</v>
+        <v>46193</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9556,7 +9551,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9599,7 +9594,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9613,10 +9608,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45849</v>
+        <v>46275</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9634,7 +9629,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9677,7 +9672,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9691,10 +9686,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45854</v>
+        <v>46275</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9712,7 +9707,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9755,7 +9750,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9769,10 +9764,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45869</v>
+        <v>46275</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9784,8 +9779,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9845,7 +9845,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17101-2023</t>
+          <t>A 12958-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45034</v>
+        <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1908,17 +1908,22 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1933,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1945,9 +1950,122 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallkötticka
+Ullticka
+Blodticka
+Vågbandad barkbock
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17101-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45034</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
         <v>4</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -1956,154 +2074,36 @@
 Trådticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 12958-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallkötticka
-Ullticka
-Blodticka
-Vågbandad barkbock
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
         <v/>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 34859-2025</t>
+          <t>A 18576-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45849</v>
+        <v>46127</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,19 +2583,14 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2622,149 +2617,154 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 34859-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Mörk husmossa
 Rostfläck</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45726</v>
+        <v>44959</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2947,42 +2947,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45133</v>
+        <v>46029</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3011,13 +3011,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3057,46 +3052,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3110,10 +3105,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44497</v>
+        <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3126,13 +3121,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3166,42 +3161,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3215,10 +3214,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46029</v>
+        <v>45133</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3230,8 +3229,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3271,46 +3275,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3324,10 +3328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46043</v>
+        <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,18 +3343,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3364,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3376,50 +3385,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3433,10 +3438,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3448,11 +3453,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3489,42 +3499,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3538,10 +3552,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44959</v>
+        <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3553,11 +3567,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3566,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3578,10 +3597,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3590,46 +3609,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3643,10 +3666,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46071</v>
+        <v>46094</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3658,22 +3681,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3688,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3700,46 +3718,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3753,10 +3775,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46092</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3768,26 +3790,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3798,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3810,50 +3827,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3867,10 +3880,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46092</v>
+        <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,25 +3895,20 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3912,10 +3920,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3928,46 +3936,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3981,10 +3985,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46094</v>
+        <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3997,20 +4001,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -4021,10 +4025,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4037,39 +4041,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 72966-2021</t>
+          <t>A 62441-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44548</v>
+        <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 72966-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5031,7 +5031,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62441-2021</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44503</v>
+        <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44518</v>
+        <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,8 +5133,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5177,7 +5182,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5191,10 +5196,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45390</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5206,13 +5211,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44518</v>
+        <v>45675</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45770</v>
+        <v>45414</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45352</v>
+        <v>44735</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5430,13 +5430,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5479,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5493,10 +5488,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45112</v>
+        <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5508,13 +5503,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5557,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5571,10 +5561,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45306</v>
+        <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5586,13 +5576,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5635,7 +5620,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5645,14 +5630,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45439</v>
+        <v>45194</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5665,7 +5650,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5708,7 +5693,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5718,14 +5703,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45922</v>
+        <v>44673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5738,7 +5723,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5781,7 +5766,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5791,14 +5776,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45931</v>
+        <v>45642</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5811,7 +5796,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5854,7 +5839,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5868,10 +5853,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45937</v>
+        <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5884,7 +5869,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5927,7 +5912,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5941,10 +5926,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44995</v>
+        <v>45307</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5957,7 +5942,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6000,7 +5985,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6014,10 +5999,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44757</v>
+        <v>45955</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6030,7 +6015,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6073,7 +6058,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6087,10 +6072,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44995</v>
+        <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6103,7 +6088,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6146,7 +6131,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6156,14 +6141,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45194</v>
+        <v>45075</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6176,7 +6161,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6219,7 +6204,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6229,14 +6214,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44993</v>
+        <v>45931</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6249,7 +6234,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6292,7 +6277,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6306,10 +6291,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44777</v>
+        <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6322,7 +6307,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6365,7 +6350,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6375,14 +6360,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44673</v>
+        <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6395,7 +6380,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6438,7 +6423,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6452,10 +6437,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45112</v>
+        <v>45843</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6467,13 +6452,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6516,7 +6496,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6530,10 +6510,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45223</v>
+        <v>46140</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6546,7 +6526,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>16.3</v>
+        <v>5.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6589,7 +6569,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6603,10 +6583,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45642</v>
+        <v>46135</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6619,7 +6599,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6662,7 +6642,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6676,10 +6656,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45075</v>
+        <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6691,8 +6671,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6735,7 +6720,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6749,10 +6734,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45414</v>
+        <v>44995</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6765,7 +6750,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6808,7 +6793,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6822,10 +6807,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45994</v>
+        <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6837,13 +6822,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6886,7 +6866,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6900,10 +6880,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45307</v>
+        <v>46043</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6916,7 +6896,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6959,7 +6939,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6973,10 +6953,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46029</v>
+        <v>46042</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6989,7 +6969,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7032,7 +7012,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7046,10 +7026,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46042</v>
+        <v>46167</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7062,7 +7042,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7105,7 +7085,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7119,10 +7099,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7135,7 +7115,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7178,7 +7158,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7195,7 +7175,7 @@
         <v>46052</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7208,7 +7188,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7251,7 +7231,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7265,10 +7245,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46052</v>
+        <v>44757</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7281,7 +7261,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7324,7 +7304,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7338,10 +7318,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45675</v>
+        <v>44777</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7354,7 +7334,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7397,7 +7377,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7411,10 +7391,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46072</v>
+        <v>45223</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7427,7 +7407,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>16.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7470,7 +7450,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7484,10 +7464,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44993</v>
+        <v>46072</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7500,7 +7480,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7543,7 +7523,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7553,14 +7533,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45187</v>
+        <v>46085</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7572,13 +7552,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7621,7 +7596,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7631,14 +7606,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46085</v>
+        <v>46091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7650,8 +7625,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7694,7 +7674,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7708,10 +7688,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7729,7 +7709,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7768,6 +7748,26 @@
         <v>0</v>
       </c>
       <c r="V80" s="2" t="inlineStr"/>
+      <c r="Z80">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA80">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB80">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC80">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD80">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
@@ -7789,7 +7789,7 @@
         <v>46092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7867,7 +7867,7 @@
         <v>46092</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7924,31 +7924,11 @@
         <v>0</v>
       </c>
       <c r="V82" s="2" t="inlineStr"/>
-      <c r="Z82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7965,7 +7945,7 @@
         <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7983,7 +7963,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8026,7 +8006,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8043,7 +8023,7 @@
         <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8061,7 +8041,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8104,7 +8084,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8118,10 +8098,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46092</v>
+        <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8133,13 +8113,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8182,7 +8157,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8196,10 +8171,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44791</v>
+        <v>44846</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8211,13 +8186,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8260,7 +8230,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8274,10 +8244,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45849</v>
+        <v>45675</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8289,13 +8259,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8338,7 +8303,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8352,10 +8317,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45854</v>
+        <v>44959</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8367,13 +8332,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8416,7 +8376,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8430,10 +8390,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44735</v>
+        <v>46135</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8446,7 +8406,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8489,7 +8449,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8503,10 +8463,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45869</v>
+        <v>44993</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8519,7 +8479,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8562,7 +8522,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8576,10 +8536,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45675</v>
+        <v>45112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8591,8 +8551,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8635,7 +8600,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8649,10 +8614,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44959</v>
+        <v>45187</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8664,8 +8629,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8708,7 +8678,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8722,10 +8692,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46135</v>
+        <v>45352</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8737,8 +8707,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8781,7 +8756,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8795,10 +8770,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44846</v>
+        <v>46255</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8810,8 +8785,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8854,7 +8834,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8868,10 +8848,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45955</v>
+        <v>46261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8883,8 +8863,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8927,7 +8912,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8941,10 +8926,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45843</v>
+        <v>45770</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8957,7 +8942,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9000,7 +8985,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9010,14 +8995,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45034</v>
+        <v>46193</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9030,7 +9015,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9073,7 +9058,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9087,10 +9072,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46140</v>
+        <v>45390</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9102,8 +9087,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9146,7 +9136,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9160,10 +9150,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46135</v>
+        <v>46275</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9175,8 +9165,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9219,7 +9214,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9233,10 +9228,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45300</v>
+        <v>46275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9248,8 +9243,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46167</v>
+        <v>46275</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9321,8 +9321,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9365,7 +9370,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9379,10 +9384,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46255</v>
+        <v>45306</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9400,7 +9405,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9443,7 +9448,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9457,10 +9462,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46261</v>
+        <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9478,7 +9483,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9521,7 +9526,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9531,14 +9536,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46193</v>
+        <v>45300</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9551,7 +9556,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.4</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9594,7 +9599,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9608,10 +9613,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46275</v>
+        <v>45439</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9623,13 +9628,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9672,7 +9672,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46275</v>
+        <v>45849</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9750,7 +9750,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46275</v>
+        <v>45854</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9845,7 +9845,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61768-2025</t>
+          <t>A 13004-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46002</v>
+        <v>46092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,20 +2358,25 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2386,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2395,265 +2400,260 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Kamjordstjärna</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 13004-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44959</v>
+        <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,42 +2947,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2996,10 +3000,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3012,7 +3016,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3048,50 +3052,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3105,10 +3109,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46043</v>
+        <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3120,18 +3124,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3145,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3157,50 +3166,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45133</v>
+        <v>46092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3235,7 +3240,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3271,50 +3276,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3328,10 +3333,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3345,23 +3350,23 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3376,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3385,46 +3390,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3438,10 +3447,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,13 +3462,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3471,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3483,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3499,46 +3503,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3552,10 +3556,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46092</v>
+        <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3567,26 +3571,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3597,10 +3596,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3609,50 +3608,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3666,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46094</v>
+        <v>44959</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3682,20 +3677,20 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3706,10 +3701,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3718,50 +3713,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3775,10 +3766,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45726</v>
+        <v>45133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,11 +3781,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3803,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3815,10 +3811,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3831,35 +3827,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44791</v>
+        <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5135,11 +5135,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>46029</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45675</v>
+        <v>46042</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45414</v>
+        <v>46043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44735</v>
+        <v>46052</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44995</v>
+        <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44993</v>
+        <v>45439</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5630,14 +5630,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45194</v>
+        <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5703,14 +5703,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44673</v>
+        <v>46072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5776,14 +5776,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45642</v>
+        <v>45931</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5849,14 +5849,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45869</v>
+        <v>46085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5912,7 +5912,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45307</v>
+        <v>44995</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5985,7 +5985,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45955</v>
+        <v>46091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6014,8 +6014,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6058,7 +6063,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6072,10 +6077,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45922</v>
+        <v>46092</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6087,8 +6092,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6131,7 +6141,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6145,10 +6155,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45075</v>
+        <v>46092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6160,8 +6170,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6200,11 +6215,31 @@
         <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
+      <c r="Z59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6214,14 +6249,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6234,7 +6269,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6277,7 +6312,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6291,10 +6326,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45937</v>
+        <v>46092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6306,8 +6341,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6350,7 +6390,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6364,10 +6404,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6379,8 +6419,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6423,7 +6468,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6437,10 +6482,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45843</v>
+        <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6452,8 +6497,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6496,7 +6546,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6510,10 +6560,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46140</v>
+        <v>44757</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6569,7 +6619,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6583,10 +6633,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46135</v>
+        <v>44995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6599,7 +6649,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6642,7 +6692,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6656,10 +6706,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45994</v>
+        <v>44993</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6671,13 +6721,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6720,7 +6765,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6734,10 +6779,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44995</v>
+        <v>44777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6795,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6793,7 +6838,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6807,10 +6852,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46029</v>
+        <v>45075</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6823,7 +6868,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6866,7 +6911,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6880,10 +6925,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46043</v>
+        <v>46135</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6896,7 +6941,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6939,7 +6984,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6953,10 +6998,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46042</v>
+        <v>45994</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6968,8 +7013,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7012,7 +7062,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7026,10 +7076,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46167</v>
+        <v>45955</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7085,7 +7135,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7099,10 +7149,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46052</v>
+        <v>45843</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7115,7 +7165,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7158,7 +7208,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7172,10 +7222,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46052</v>
+        <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7188,7 +7238,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7231,7 +7281,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7245,10 +7295,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44757</v>
+        <v>46140</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7304,7 +7354,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7318,10 +7368,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44777</v>
+        <v>46135</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7334,7 +7384,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7377,7 +7427,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7391,10 +7441,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45223</v>
+        <v>44518</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7407,7 +7457,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>16.3</v>
+        <v>6.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7450,7 +7500,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7464,10 +7514,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46072</v>
+        <v>45849</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7479,8 +7529,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7523,7 +7578,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7533,14 +7588,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46085</v>
+        <v>45854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7552,8 +7607,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7596,7 +7656,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7610,10 +7670,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46091</v>
+        <v>46167</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7625,13 +7685,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7674,7 +7729,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7688,10 +7743,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46092</v>
+        <v>45770</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7703,13 +7758,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7748,31 +7798,11 @@
         <v>0</v>
       </c>
       <c r="V80" s="2" t="inlineStr"/>
-      <c r="Z80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7786,10 +7816,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46092</v>
+        <v>45352</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7807,7 +7837,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7850,7 +7880,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7864,10 +7894,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46092</v>
+        <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7885,7 +7915,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7928,7 +7958,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7942,10 +7972,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46092</v>
+        <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7963,7 +7993,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8006,7 +8036,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8020,10 +8050,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46092</v>
+        <v>45869</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8035,13 +8065,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8084,7 +8109,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8094,14 +8119,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44518</v>
+        <v>45194</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8114,7 +8139,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8157,7 +8182,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8167,14 +8192,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44846</v>
+        <v>44673</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8187,7 +8212,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8230,7 +8255,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8244,10 +8269,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45675</v>
+        <v>45112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8259,8 +8284,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8303,7 +8333,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8317,10 +8347,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44959</v>
+        <v>46255</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8332,8 +8362,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8376,7 +8411,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8390,10 +8425,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46135</v>
+        <v>45223</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8406,7 +8441,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.2</v>
+        <v>16.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8449,7 +8484,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8463,10 +8498,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44993</v>
+        <v>45642</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8479,7 +8514,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8522,7 +8557,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8536,10 +8571,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45112</v>
+        <v>46261</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8557,7 +8592,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8600,7 +8635,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8614,10 +8649,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45187</v>
+        <v>45414</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8629,13 +8664,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8678,7 +8708,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8692,10 +8722,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45352</v>
+        <v>45307</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8705,11 +8735,6 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -8756,7 +8781,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8766,14 +8791,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46255</v>
+        <v>46193</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8785,13 +8810,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8834,7 +8854,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8848,10 +8868,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8869,7 +8889,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8912,7 +8932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8926,10 +8946,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45770</v>
+        <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8941,8 +8961,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8985,7 +9010,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8995,14 +9020,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46193</v>
+        <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9014,8 +9039,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9058,7 +9088,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9072,10 +9102,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45390</v>
+        <v>45675</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9087,13 +9117,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9136,7 +9161,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9150,10 +9175,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46275</v>
+        <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9165,13 +9190,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9214,7 +9234,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9228,10 +9248,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46275</v>
+        <v>45187</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9245,11 +9265,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9292,7 +9312,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9306,10 +9326,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46275</v>
+        <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9323,11 +9343,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9370,7 +9390,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9384,10 +9404,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45306</v>
+        <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9399,13 +9419,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9448,7 +9463,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9462,10 +9477,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45112</v>
+        <v>45675</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9477,13 +9492,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9526,7 +9536,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9540,10 +9550,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45300</v>
+        <v>44959</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9556,7 +9566,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9599,7 +9609,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9613,10 +9623,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45439</v>
+        <v>44846</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9629,7 +9639,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9672,7 +9682,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9686,10 +9696,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45849</v>
+        <v>45034</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9701,13 +9711,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9750,7 +9755,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9764,10 +9769,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45854</v>
+        <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9779,13 +9784,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9845,7 +9845,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46002</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>46092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44959</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>46029</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>46042</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>46043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>46052</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45439</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45931</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>46085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44995</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>46091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>46092</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>46092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>46092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44757</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44993</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>44777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45075</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>46135</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45994</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45955</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>45843</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>46140</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46135</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44518</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45849</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>45854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>46167</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45770</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45352</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45869</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45194</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44673</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>46255</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45223</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45642</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>46261</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45414</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45307</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>46193</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>46275</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45675</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45187</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45675</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>44959</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44846</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45034</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>46127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46002</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>46092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44959</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>46029</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>46042</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>46043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>46052</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>45439</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>46072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45931</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>46085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44995</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>46091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>46092</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>46092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>46092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44757</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>44993</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>44777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45075</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>46135</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45994</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45955</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>45843</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>46140</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46135</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44518</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45849</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>45854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>46167</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45770</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45352</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45869</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45194</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44673</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>46255</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45223</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45642</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>46261</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45414</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45307</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>46193</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>46275</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45675</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>45187</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45675</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>44959</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44846</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45034</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE108"/>
+  <dimension ref="A1:AE109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13004-2026</t>
+          <t>A 61768-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46092</v>
+        <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,25 +2358,20 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2391,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2400,371 +2395,376 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 34859-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Mörk husmossa
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 13004-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 18576-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>4.8</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Kransmossa</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 61768-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 34859-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45849</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Mörk husmossa
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46029</v>
+        <v>44959</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,20 +2907,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,46 +2947,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3000,10 +2996,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46043</v>
+        <v>46029</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3016,7 +3012,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3052,50 +3048,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3109,10 +3105,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46071</v>
+        <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3124,22 +3120,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3154,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3166,46 +3157,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46092</v>
+        <v>46071</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3236,21 +3231,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3264,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3276,43 +3271,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
@@ -3336,7 +3327,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3433,7 +3424,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3447,10 +3438,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,8 +3453,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3503,46 +3499,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3556,10 +3552,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45726</v>
+        <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3572,10 +3568,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3584,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3596,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3608,46 +3604,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44959</v>
+        <v>45133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,11 +3676,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3689,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3701,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3717,42 +3722,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3766,10 +3775,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45133</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3781,26 +3790,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3811,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3827,39 +3831,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5135,11 +5135,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46029</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46042</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46043</v>
+        <v>45675</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46052</v>
+        <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46052</v>
+        <v>45414</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5564,7 +5564,7 @@
         <v>45439</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45922</v>
+        <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46072</v>
+        <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45931</v>
+        <v>45194</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5849,14 +5849,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46085</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5912,7 +5912,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5922,14 +5922,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44995</v>
+        <v>45931</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5985,7 +5985,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46091</v>
+        <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6014,13 +6014,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6063,7 +6058,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6077,10 +6072,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46092</v>
+        <v>45849</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6098,7 +6093,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6141,7 +6136,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6151,14 +6146,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46092</v>
+        <v>44673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6168,11 +6163,6 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -6215,31 +6205,11 @@
         <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
-      <c r="Z59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6253,10 +6223,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45937</v>
+        <v>45854</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6268,8 +6238,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6312,7 +6287,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6326,10 +6301,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46092</v>
+        <v>46029</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6341,13 +6316,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6390,7 +6360,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6404,10 +6374,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46092</v>
+        <v>45869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6419,13 +6389,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6468,7 +6433,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6482,10 +6447,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46092</v>
+        <v>45642</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6497,13 +6462,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6546,7 +6506,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6560,10 +6520,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44757</v>
+        <v>46043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6576,7 +6536,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6619,7 +6579,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6633,10 +6593,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44995</v>
+        <v>46042</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6649,7 +6609,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6692,7 +6652,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6706,10 +6666,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44993</v>
+        <v>45307</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6765,7 +6725,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6779,10 +6739,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44777</v>
+        <v>45994</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6794,8 +6754,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6838,7 +6803,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6852,10 +6817,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45075</v>
+        <v>46052</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6868,7 +6833,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6911,7 +6876,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6925,10 +6890,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46135</v>
+        <v>46052</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6941,7 +6906,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6984,7 +6949,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6998,10 +6963,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45994</v>
+        <v>46072</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7011,11 +6976,6 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -7062,7 +7022,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7076,10 +7036,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45955</v>
+        <v>45075</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7092,7 +7052,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7135,7 +7095,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7145,14 +7105,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45843</v>
+        <v>46085</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7165,7 +7125,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7208,7 +7168,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7222,10 +7182,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44518</v>
+        <v>46091</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7237,8 +7197,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7281,7 +7246,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7295,10 +7260,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46140</v>
+        <v>46092</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7310,8 +7275,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7350,11 +7320,31 @@
         <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr"/>
+      <c r="Z74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD74">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7368,10 +7358,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46135</v>
+        <v>46092</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7383,8 +7373,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7427,7 +7422,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7441,10 +7436,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7456,8 +7451,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7500,7 +7500,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7514,10 +7514,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45849</v>
+        <v>46092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7578,7 +7578,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7592,10 +7592,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45854</v>
+        <v>46092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7656,7 +7656,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46167</v>
+        <v>44518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7729,7 +7729,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45770</v>
+        <v>46135</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7802,7 +7802,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45352</v>
+        <v>44995</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7831,13 +7831,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7880,7 +7875,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7894,10 +7889,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45112</v>
+        <v>45955</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7909,13 +7904,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7958,7 +7948,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7972,10 +7962,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45306</v>
+        <v>45843</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7987,13 +7977,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8036,7 +8021,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8050,10 +8035,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45869</v>
+        <v>46140</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8066,7 +8051,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8109,7 +8094,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8119,14 +8104,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45194</v>
+        <v>46135</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8139,7 +8124,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8182,7 +8167,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8192,14 +8177,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44673</v>
+        <v>44757</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8212,7 +8197,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8255,7 +8240,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8269,10 +8254,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45112</v>
+        <v>44777</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8284,13 +8269,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8333,7 +8313,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8347,10 +8327,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46255</v>
+        <v>45223</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8362,13 +8342,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>7.6</v>
+        <v>16.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8411,7 +8386,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8425,10 +8400,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45223</v>
+        <v>46167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8441,7 +8416,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>16.3</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8484,7 +8459,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8498,10 +8473,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45642</v>
+        <v>44518</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8514,7 +8489,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8557,7 +8532,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8571,10 +8546,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46261</v>
+        <v>44846</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8586,13 +8561,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8635,7 +8605,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8649,10 +8619,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45414</v>
+        <v>45675</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8665,7 +8635,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8708,7 +8678,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8722,10 +8692,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45307</v>
+        <v>44959</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8738,7 +8708,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8781,7 +8751,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8791,14 +8761,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46193</v>
+        <v>44993</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8811,7 +8781,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8854,7 +8824,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8868,10 +8838,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46275</v>
+        <v>45112</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8889,7 +8859,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8932,7 +8902,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8946,10 +8916,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46275</v>
+        <v>45187</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8963,11 +8933,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9010,7 +8980,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9024,10 +8994,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46275</v>
+        <v>45352</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9045,7 +9015,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9088,7 +9058,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9102,10 +9072,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45675</v>
+        <v>46255</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9117,8 +9087,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9161,7 +9136,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9175,10 +9150,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44993</v>
+        <v>45770</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9191,7 +9166,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9234,7 +9209,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9248,10 +9223,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45187</v>
+        <v>46261</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9265,11 +9240,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9312,7 +9287,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9326,10 +9301,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44791</v>
+        <v>45390</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9343,11 +9318,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9390,7 +9365,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9400,14 +9375,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44735</v>
+        <v>46193</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9420,7 +9395,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9463,7 +9438,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9477,10 +9452,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45675</v>
+        <v>46275</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9492,8 +9467,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9536,7 +9516,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9550,10 +9530,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44959</v>
+        <v>46275</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9565,8 +9545,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9609,7 +9594,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9623,10 +9608,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44846</v>
+        <v>46275</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9638,8 +9623,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9682,7 +9672,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9696,10 +9686,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45034</v>
+        <v>45306</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9711,8 +9701,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9755,7 +9750,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9769,134 +9764,217 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45300</v>
+        <v>45112</v>
       </c>
       <c r="E107" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>A 39978-2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="E108" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>S 1411-2022</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D108" s="1" t="n">
+      <c r="D109" s="1" t="n">
         <v>44634</v>
       </c>
-      <c r="E108" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
+      <c r="E109" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
         <v>2</v>
       </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" s="2" t="inlineStr"/>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61768-2025</t>
+          <t>A 34859-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46002</v>
+        <v>45849</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,17 +2358,22 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2383,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2399,147 +2404,142 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>Mörk husmossa
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>Gullpudra
 Kamjordstjärna</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 34859-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45849</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mörk husmossa
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
         <v>46092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>46127</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44959</v>
+        <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,42 +2947,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2996,10 +3000,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46029</v>
+        <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3012,7 +3016,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3048,50 +3052,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3105,10 +3109,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46043</v>
+        <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3120,18 +3124,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3145,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3157,50 +3166,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3214,10 +3219,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46071</v>
+        <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3229,13 +3234,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3244,10 +3244,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3275,42 +3275,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3327,7 +3327,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3369,10 +3369,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3385,46 +3385,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3441,7 +3441,7 @@
         <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3483,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3499,39 +3499,39 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
         <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45133</v>
+        <v>44959</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,26 +3676,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3706,10 +3701,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3722,46 +3717,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3775,10 +3766,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45726</v>
+        <v>45133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3790,11 +3781,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3803,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3815,10 +3811,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3831,35 +3827,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44791</v>
+        <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5135,11 +5135,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>46029</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>45439</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45675</v>
+        <v>45922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45300</v>
+        <v>46042</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5484,14 +5484,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45414</v>
+        <v>45931</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45439</v>
+        <v>46043</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
         <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44993</v>
+        <v>45937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5776,14 +5776,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45194</v>
+        <v>45849</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5795,8 +5795,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5839,7 +5844,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5853,10 +5858,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45922</v>
+        <v>45854</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5868,8 +5873,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5912,7 +5922,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5922,14 +5932,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45931</v>
+        <v>44757</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5942,7 +5952,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5985,7 +5995,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5999,10 +6009,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45937</v>
+        <v>44995</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6015,7 +6025,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6058,7 +6068,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6072,10 +6082,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45849</v>
+        <v>44993</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6087,13 +6097,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6136,7 +6141,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6146,14 +6151,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44673</v>
+        <v>45869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6166,7 +6171,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6209,7 +6214,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6223,10 +6228,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45854</v>
+        <v>44777</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6238,13 +6243,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6287,7 +6287,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46029</v>
+        <v>46052</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6360,7 +6360,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45869</v>
+        <v>46052</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6433,7 +6433,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45642</v>
+        <v>45075</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46043</v>
+        <v>46072</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46042</v>
+        <v>45994</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6608,8 +6608,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6652,7 +6657,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6662,14 +6667,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45307</v>
+        <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6682,7 +6687,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6725,7 +6730,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6739,10 +6744,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45994</v>
+        <v>46091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6760,7 +6765,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6803,7 +6808,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6817,10 +6822,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46052</v>
+        <v>46092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6832,8 +6837,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6876,7 +6886,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6890,10 +6900,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46052</v>
+        <v>46092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6905,8 +6915,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6945,11 +6960,31 @@
         <v>0</v>
       </c>
       <c r="V69" s="2" t="inlineStr"/>
+      <c r="Z69">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA69">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB69">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC69">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD69">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6963,10 +6998,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46072</v>
+        <v>46092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6978,8 +7013,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7022,7 +7062,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7036,10 +7076,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45075</v>
+        <v>46092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7051,8 +7091,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7095,7 +7140,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7105,14 +7150,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7124,8 +7169,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7168,7 +7218,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7182,10 +7232,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46091</v>
+        <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7197,13 +7247,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7246,7 +7291,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7260,10 +7305,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46092</v>
+        <v>46135</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7275,13 +7320,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7320,31 +7360,11 @@
         <v>0</v>
       </c>
       <c r="V74" s="2" t="inlineStr"/>
-      <c r="Z74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD74">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7358,10 +7378,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46092</v>
+        <v>44518</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7373,13 +7393,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7422,7 +7437,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7436,10 +7451,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46092</v>
+        <v>45770</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7451,13 +7466,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7500,7 +7510,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7514,10 +7524,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46092</v>
+        <v>45352</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7535,7 +7545,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7578,7 +7588,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7592,10 +7602,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46092</v>
+        <v>45112</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7613,7 +7623,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7656,7 +7666,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7670,10 +7680,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44518</v>
+        <v>45955</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7686,7 +7696,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7729,7 +7739,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7743,10 +7753,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46135</v>
+        <v>45306</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7758,8 +7768,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7802,7 +7817,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7816,10 +7831,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44995</v>
+        <v>45843</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7847,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7875,7 +7890,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7889,10 +7904,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45955</v>
+        <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7920,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7948,7 +7963,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7962,10 +7977,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45843</v>
+        <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7993,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8021,7 +8036,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8031,14 +8046,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46140</v>
+        <v>45194</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8066,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8094,7 +8109,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8104,14 +8119,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46135</v>
+        <v>44673</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8167,7 +8182,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8181,10 +8196,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44757</v>
+        <v>45112</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8196,8 +8211,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8240,7 +8260,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8254,10 +8274,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44777</v>
+        <v>45223</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8290,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>16.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8313,7 +8333,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8327,10 +8347,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45223</v>
+        <v>45642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8343,7 +8363,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>16.3</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8403,7 +8423,7 @@
         <v>46167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8459,7 +8479,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8473,10 +8493,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44518</v>
+        <v>45414</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8489,7 +8509,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8532,7 +8552,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8546,10 +8566,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44846</v>
+        <v>45307</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8562,7 +8582,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8605,7 +8625,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8622,7 +8642,7 @@
         <v>45675</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8635,7 +8655,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8678,7 +8698,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8692,10 +8712,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44959</v>
+        <v>44993</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8708,7 +8728,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8751,7 +8771,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8765,10 +8785,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44993</v>
+        <v>45187</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8780,8 +8800,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8824,7 +8849,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8838,10 +8863,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45112</v>
+        <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8855,11 +8880,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8902,7 +8927,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8916,10 +8941,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45187</v>
+        <v>46255</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8933,11 +8958,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8980,7 +9005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8994,10 +9019,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45352</v>
+        <v>44735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9009,13 +9034,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9058,7 +9078,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9072,10 +9092,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9093,7 +9113,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9136,7 +9156,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9150,10 +9170,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45770</v>
+        <v>45675</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9166,7 +9186,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9209,7 +9229,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9223,10 +9243,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46261</v>
+        <v>44959</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9238,13 +9258,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9287,7 +9302,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9297,14 +9312,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45390</v>
+        <v>46193</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9316,13 +9331,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9365,7 +9375,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9375,14 +9385,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46193</v>
+        <v>46275</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9394,8 +9404,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9438,7 +9453,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9455,7 +9470,7 @@
         <v>46275</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9473,7 +9488,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9516,7 +9531,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9533,7 +9548,7 @@
         <v>46275</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9551,7 +9566,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9594,7 +9609,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9608,10 +9623,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46275</v>
+        <v>44846</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9623,13 +9638,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9672,7 +9682,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9686,10 +9696,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45306</v>
+        <v>45034</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9701,13 +9711,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9750,7 +9755,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9764,10 +9769,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45112</v>
+        <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9779,13 +9784,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9845,7 +9845,7 @@
         <v>46293</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 12958-2026</t>
+          <t>A 17101-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46092</v>
+        <v>45034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1908,22 +1908,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1938,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1950,9 +1945,127 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Ullticka
+Grön sköldmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 12958-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallkötticka
 Ullticka
@@ -1961,149 +2074,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17101-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45034</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Ullticka
-Grön sköldmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
         <v/>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45849</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>46002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>46127</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46029</v>
+        <v>45133</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2906,8 +2906,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2947,46 +2952,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3000,10 +3005,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46043</v>
+        <v>44518</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3016,20 +3021,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -3040,10 +3045,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3056,46 +3061,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 2171-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3109,10 +3110,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46071</v>
+        <v>45309</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3126,20 +3127,20 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3154,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3166,39 +3167,39 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
         <v/>
       </c>
     </row>
@@ -3222,7 +3223,7 @@
         <v>45726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3310,7 +3311,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3324,10 +3325,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46092</v>
+        <v>44497</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3339,19 +3340,14 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3385,46 +3381,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3438,10 +3430,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>44959</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,16 +3445,11 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3495,50 +3482,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3552,10 +3535,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46094</v>
+        <v>46029</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3568,7 +3551,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3604,50 +3587,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3644,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44959</v>
+        <v>46043</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3677,10 +3660,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3689,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3701,10 +3684,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3713,46 +3696,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3766,10 +3753,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45133</v>
+        <v>46071</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3783,21 +3770,21 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3811,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3827,46 +3814,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3880,10 +3863,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44497</v>
+        <v>46092</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3895,21 +3878,26 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
@@ -3920,10 +3908,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3936,42 +3924,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3985,10 +3977,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4000,11 +3992,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -4013,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4025,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4041,42 +4038,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2171-2024</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4090,10 +4091,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45309</v>
+        <v>46094</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,13 +4106,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4151,35 +4147,39 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64044-2021</t>
+          <t>A 70275-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44510</v>
+        <v>44536</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4617,8 +4617,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4661,7 +4666,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 70275-2021</t>
+          <t>A 64044-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4675,10 +4680,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44536</v>
+        <v>44510</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4690,13 +4695,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18820-2022</t>
+          <t>A 62441-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44690</v>
+        <v>44503</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62441-2021</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44503</v>
+        <v>44548</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 18820-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44548</v>
+        <v>44690</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>45642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,13 +5133,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5177,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5191,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46029</v>
+        <v>44791</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5211,8 +5206,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45439</v>
+        <v>44757</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45922</v>
+        <v>44777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46042</v>
+        <v>45307</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5484,14 +5484,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45931</v>
+        <v>45223</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>16.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46043</v>
+        <v>45390</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5576,8 +5576,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5620,7 +5625,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5634,10 +5639,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44995</v>
+        <v>45034</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5650,7 +5655,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5693,7 +5698,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45937</v>
+        <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5723,7 +5728,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5766,7 +5771,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5780,10 +5785,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45849</v>
+        <v>44846</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5795,13 +5800,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5844,7 +5844,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45854</v>
+        <v>45306</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44757</v>
+        <v>44735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6009,10 +6009,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44995</v>
+        <v>45675</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6068,7 +6068,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44993</v>
+        <v>45414</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6141,7 +6141,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45869</v>
+        <v>45112</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6170,8 +6170,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6214,7 +6219,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6228,10 +6233,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44777</v>
+        <v>45675</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6244,7 +6249,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6287,7 +6292,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6301,10 +6306,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46052</v>
+        <v>44959</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6317,7 +6322,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6360,7 +6365,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6374,10 +6379,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46052</v>
+        <v>45075</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6390,7 +6395,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6433,7 +6438,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6447,10 +6452,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45075</v>
+        <v>45300</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6463,7 +6468,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6506,7 +6511,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6520,10 +6525,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46072</v>
+        <v>44993</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6536,7 +6541,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6579,7 +6584,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6593,10 +6598,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45994</v>
+        <v>44518</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6608,13 +6613,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6657,7 +6657,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6667,14 +6667,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46085</v>
+        <v>45112</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6686,8 +6686,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6730,7 +6735,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6744,10 +6749,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46091</v>
+        <v>44995</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6759,13 +6764,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6808,7 +6808,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46092</v>
+        <v>45439</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6837,13 +6837,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6886,7 +6881,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6900,10 +6895,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46092</v>
+        <v>45187</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6917,11 +6912,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6960,31 +6955,11 @@
         <v>0</v>
       </c>
       <c r="V69" s="2" t="inlineStr"/>
-      <c r="Z69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6998,10 +6973,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46092</v>
+        <v>44993</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7013,13 +6988,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7062,7 +7032,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7072,14 +7042,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46092</v>
+        <v>45194</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7091,13 +7061,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7140,7 +7105,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7154,10 +7119,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46092</v>
+        <v>45352</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7175,7 +7140,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7218,7 +7183,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7232,10 +7197,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44518</v>
+        <v>44995</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7248,7 +7213,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7291,7 +7256,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7305,10 +7270,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46135</v>
+        <v>45770</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7321,7 +7286,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7364,7 +7329,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7378,10 +7343,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44518</v>
+        <v>45849</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7393,8 +7358,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7437,7 +7407,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7451,10 +7421,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45770</v>
+        <v>45854</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7466,8 +7436,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7510,7 +7485,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7524,10 +7499,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45352</v>
+        <v>45869</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7537,11 +7512,6 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -7588,7 +7558,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7598,14 +7568,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45112</v>
+        <v>44673</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7617,13 +7587,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7666,7 +7631,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7680,10 +7645,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45955</v>
+        <v>45937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7696,7 +7661,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7739,7 +7704,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7753,10 +7718,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45306</v>
+        <v>45922</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7768,13 +7733,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7817,7 +7777,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7827,14 +7787,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45843</v>
+        <v>45931</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7847,7 +7807,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7890,7 +7850,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7904,10 +7864,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46140</v>
+        <v>45994</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7919,8 +7879,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7963,7 +7928,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7977,10 +7942,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46135</v>
+        <v>46029</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7993,7 +7958,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8036,7 +8001,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8046,14 +8011,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45194</v>
+        <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8066,7 +8031,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8109,7 +8074,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8119,14 +8084,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44673</v>
+        <v>46042</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8182,7 +8147,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8196,10 +8161,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45112</v>
+        <v>46052</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8209,11 +8174,6 @@
       <c r="G86" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -8260,7 +8220,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8274,10 +8234,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45223</v>
+        <v>46052</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8290,7 +8250,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>16.3</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8333,7 +8293,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8347,10 +8307,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45642</v>
+        <v>46072</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8363,7 +8323,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8406,7 +8366,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8416,14 +8376,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46167</v>
+        <v>46085</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8436,7 +8396,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8479,7 +8439,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8493,10 +8453,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45414</v>
+        <v>46091</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8508,8 +8468,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8552,7 +8517,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8566,10 +8531,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45307</v>
+        <v>46092</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8581,8 +8546,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8621,11 +8591,31 @@
         <v>0</v>
       </c>
       <c r="V91" s="2" t="inlineStr"/>
+      <c r="Z91">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA91">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB91">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC91">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD91">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8639,10 +8629,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45675</v>
+        <v>46092</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8654,8 +8644,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8698,7 +8693,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8712,10 +8707,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44993</v>
+        <v>46092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8727,8 +8722,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45187</v>
+        <v>46092</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8802,11 +8802,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8849,7 +8849,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44791</v>
+        <v>46092</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8880,11 +8880,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8927,7 +8927,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46255</v>
+        <v>46135</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8956,13 +8956,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9005,7 +9000,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9019,10 +9014,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44735</v>
+        <v>45955</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9035,7 +9030,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9078,7 +9073,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9092,10 +9087,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46261</v>
+        <v>45843</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9107,13 +9102,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9156,7 +9146,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9170,10 +9160,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45675</v>
+        <v>46140</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9186,7 +9176,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9229,7 +9219,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9243,10 +9233,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44959</v>
+        <v>46135</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9259,7 +9249,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9302,7 +9292,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9312,14 +9302,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46193</v>
+        <v>46167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9332,7 +9322,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9375,7 +9365,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9389,10 +9379,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46275</v>
+        <v>46255</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9410,7 +9400,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9453,7 +9443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9467,10 +9457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46275</v>
+        <v>46261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9488,7 +9478,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9531,7 +9521,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9541,14 +9531,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46275</v>
+        <v>46193</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9560,13 +9550,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9609,7 +9594,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9623,10 +9608,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44846</v>
+        <v>46275</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9638,8 +9623,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9682,7 +9672,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9696,10 +9686,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45034</v>
+        <v>46275</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9711,8 +9701,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9755,7 +9750,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9769,10 +9764,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45300</v>
+        <v>46275</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9784,8 +9779,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9845,7 +9845,7 @@
         <v>46293</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17101-2023</t>
+          <t>A 12958-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45034</v>
+        <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1908,17 +1908,22 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1933,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1945,9 +1950,122 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Tallkötticka
+Ullticka
+Blodticka
+Vågbandad barkbock
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17101-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45034</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
         <v>4</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -1956,154 +2074,36 @@
 Trådticka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 12958-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Tallkötticka
-Ullticka
-Blodticka
-Vågbandad barkbock
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
         <v/>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 34859-2025</t>
+          <t>A 13004-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45849</v>
+        <v>46092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2388,10 +2388,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2400,371 +2400,371 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 34859-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Mörk husmossa
 Rostfläck</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 61768-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 13004-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Z18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45133</v>
+        <v>46029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2906,13 +2906,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2952,46 +2947,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3005,10 +3000,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44518</v>
+        <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3021,10 +3016,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -3033,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -3045,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3061,42 +3056,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2171-2024</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3110,10 +3109,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45309</v>
+        <v>46071</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3127,21 +3126,21 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3155,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3167,46 +3166,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3220,10 +3219,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45726</v>
+        <v>46092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3235,11 +3234,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3248,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3260,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3272,46 +3276,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3325,10 +3333,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44497</v>
+        <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3340,21 +3348,26 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -3365,10 +3378,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3381,42 +3394,46 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3430,10 +3447,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44959</v>
+        <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3446,10 +3463,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3458,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3470,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3482,46 +3499,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3535,10 +3556,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46029</v>
+        <v>45726</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3551,20 +3572,20 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3575,10 +3596,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3591,46 +3612,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3644,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46043</v>
+        <v>44959</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3660,20 +3677,20 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3684,10 +3701,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3696,50 +3713,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3753,10 +3766,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46071</v>
+        <v>45133</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3770,20 +3783,20 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3798,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3814,42 +3827,46 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3863,10 +3880,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46092</v>
+        <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3878,25 +3895,20 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3908,10 +3920,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3924,46 +3936,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3977,10 +3985,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46092</v>
+        <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3992,26 +4000,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -4022,10 +4025,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4038,46 +4041,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 2171-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4091,10 +4090,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46094</v>
+        <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,8 +4105,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4147,39 +4151,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
         <v/>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 70275-2021</t>
+          <t>A 64044-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44536</v>
+        <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4617,13 +4617,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4666,7 +4661,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64044-2021</t>
+          <t>A 70275-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4680,10 +4675,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44510</v>
+        <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4695,8 +4690,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62441-2021</t>
+          <t>A 18820-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44503</v>
+        <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 62441-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44548</v>
+        <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18820-2022</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44690</v>
+        <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45642</v>
+        <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,8 +5133,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5177,7 +5182,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5191,10 +5196,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44791</v>
+        <v>46029</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5206,13 +5211,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44757</v>
+        <v>46042</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44777</v>
+        <v>46043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45307</v>
+        <v>46052</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45223</v>
+        <v>46052</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>16.3</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45390</v>
+        <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5576,13 +5576,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5625,7 +5620,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5639,10 +5634,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45034</v>
+        <v>45439</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5655,7 +5650,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5698,7 +5693,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44518</v>
+        <v>46072</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5728,7 +5723,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5771,7 +5766,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5781,14 +5776,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44846</v>
+        <v>45931</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5801,7 +5796,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5844,7 +5839,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5854,14 +5849,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45306</v>
+        <v>46085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5873,13 +5868,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5922,7 +5912,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5936,10 +5926,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44735</v>
+        <v>45937</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5952,7 +5942,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5995,7 +5985,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6009,10 +5999,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45675</v>
+        <v>46091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6024,8 +6014,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6068,7 +6063,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6082,10 +6077,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45414</v>
+        <v>46092</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6097,8 +6092,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6141,7 +6141,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45112</v>
+        <v>46092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6215,11 +6215,31 @@
         <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
+      <c r="Z59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6233,10 +6253,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45675</v>
+        <v>46092</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6248,8 +6268,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6292,7 +6317,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6306,10 +6331,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44959</v>
+        <v>46092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6321,8 +6346,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6365,7 +6395,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6379,10 +6409,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45075</v>
+        <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6394,8 +6424,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6438,7 +6473,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6452,10 +6487,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45300</v>
+        <v>44995</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6468,7 +6503,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6511,7 +6546,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6525,10 +6560,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44993</v>
+        <v>44757</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6541,7 +6576,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6584,7 +6619,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6598,10 +6633,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44518</v>
+        <v>44995</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6614,7 +6649,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6657,7 +6692,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6671,10 +6706,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45112</v>
+        <v>44993</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6686,13 +6721,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6735,7 +6765,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6749,10 +6779,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44995</v>
+        <v>44777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6765,7 +6795,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6808,7 +6838,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6822,10 +6852,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45439</v>
+        <v>45075</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6838,7 +6868,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6881,7 +6911,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6895,10 +6925,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45187</v>
+        <v>46135</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6910,13 +6940,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6959,7 +6984,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6973,10 +6998,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44993</v>
+        <v>45994</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6988,8 +7013,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7032,7 +7062,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7042,14 +7072,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45194</v>
+        <v>45955</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7062,7 +7092,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7105,7 +7135,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7119,10 +7149,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45352</v>
+        <v>45843</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7134,13 +7164,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7183,7 +7208,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7197,10 +7222,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44995</v>
+        <v>45849</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7212,8 +7237,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7256,7 +7286,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7270,10 +7300,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45770</v>
+        <v>45854</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7285,8 +7315,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7329,7 +7364,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7343,10 +7378,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45849</v>
+        <v>44518</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7358,13 +7393,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7407,7 +7437,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7421,10 +7451,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45854</v>
+        <v>45869</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7436,13 +7466,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7485,7 +7510,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7499,10 +7524,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45869</v>
+        <v>46140</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7515,7 +7540,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7558,7 +7583,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7568,14 +7593,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44673</v>
+        <v>46135</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7631,7 +7656,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7645,10 +7670,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45937</v>
+        <v>44518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7661,7 +7686,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7704,7 +7729,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7718,10 +7743,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45922</v>
+        <v>45770</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7777,7 +7802,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7787,14 +7812,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45931</v>
+        <v>45352</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7806,8 +7831,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7850,7 +7880,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7864,10 +7894,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45994</v>
+        <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7885,7 +7915,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7928,7 +7958,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7942,10 +7972,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46029</v>
+        <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7957,8 +7987,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8001,7 +8036,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8015,10 +8050,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46043</v>
+        <v>46167</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8031,7 +8066,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8074,7 +8109,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8084,14 +8119,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46042</v>
+        <v>45194</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8104,7 +8139,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8147,7 +8182,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8157,14 +8192,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46052</v>
+        <v>44673</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8177,7 +8212,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8220,7 +8255,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8234,10 +8269,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46052</v>
+        <v>45112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8249,8 +8284,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8293,7 +8333,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8307,10 +8347,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46072</v>
+        <v>45223</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8323,7 +8363,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>16.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8366,7 +8406,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8376,14 +8416,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46085</v>
+        <v>45642</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8396,7 +8436,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8439,7 +8479,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8453,10 +8493,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46091</v>
+        <v>45414</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8468,13 +8508,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8517,7 +8552,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8531,10 +8566,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46092</v>
+        <v>46255</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8552,7 +8587,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8591,31 +8626,11 @@
         <v>0</v>
       </c>
       <c r="V91" s="2" t="inlineStr"/>
-      <c r="Z91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD91">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8629,10 +8644,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46092</v>
+        <v>45307</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8644,13 +8659,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8693,7 +8703,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8707,10 +8717,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46092</v>
+        <v>46261</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8728,7 +8738,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>7.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8771,7 +8781,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8785,10 +8795,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46092</v>
+        <v>45675</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8800,13 +8810,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8849,7 +8854,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8859,14 +8864,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46092</v>
+        <v>46193</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8878,13 +8883,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8927,7 +8927,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46135</v>
+        <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8956,8 +8956,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9000,7 +9005,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9014,10 +9019,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45955</v>
+        <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9029,8 +9034,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9073,7 +9083,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9087,10 +9097,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45843</v>
+        <v>44993</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9103,7 +9113,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9146,7 +9156,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9160,10 +9170,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46140</v>
+        <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9175,8 +9185,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9219,7 +9234,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9233,10 +9248,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46135</v>
+        <v>46275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9248,8 +9263,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9292,7 +9312,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9306,10 +9326,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46167</v>
+        <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9321,8 +9341,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9365,7 +9390,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9379,10 +9404,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46255</v>
+        <v>44735</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9394,13 +9419,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9443,7 +9463,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9457,10 +9477,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46261</v>
+        <v>45675</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9472,13 +9492,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9521,7 +9536,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 39978-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9531,14 +9546,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46193</v>
+        <v>46293</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9550,8 +9565,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9594,7 +9614,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9608,10 +9628,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46275</v>
+        <v>44959</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9623,13 +9643,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9672,7 +9687,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9686,10 +9701,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46275</v>
+        <v>44846</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9701,13 +9716,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9750,7 +9760,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9764,10 +9774,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46275</v>
+        <v>45034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9779,13 +9789,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9828,7 +9833,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 39978-2026</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9842,10 +9847,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46293</v>
+        <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9857,13 +9862,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9923,7 +9923,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13004-2026</t>
+          <t>A 61768-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46092</v>
+        <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,25 +2358,20 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2391,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2400,260 +2395,265 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 13004-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Z16">
+      <c r="Z17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 18576-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>4.8</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>7</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Kransmossa</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 61768-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46029</v>
+        <v>44959</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,20 +2907,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2947,46 +2947,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3000,10 +2996,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46043</v>
+        <v>46029</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3016,7 +3012,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3052,50 +3048,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3109,10 +3105,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46071</v>
+        <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3124,22 +3120,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3154,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3166,46 +3157,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46092</v>
+        <v>46071</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3236,21 +3231,21 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3264,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3276,43 +3271,39 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
@@ -3336,7 +3327,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3433,7 +3424,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3447,10 +3438,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,8 +3453,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3503,46 +3499,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3556,10 +3552,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45726</v>
+        <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3572,10 +3568,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3584,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3596,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3608,46 +3604,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44959</v>
+        <v>45133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,11 +3676,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3689,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3701,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3717,42 +3722,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3766,10 +3775,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45133</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3781,26 +3790,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3811,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3827,39 +3831,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5135,11 +5135,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46029</v>
+        <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46042</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46043</v>
+        <v>45675</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46052</v>
+        <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46052</v>
+        <v>45414</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45922</v>
+        <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45439</v>
+        <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5693,7 +5693,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46072</v>
+        <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5776,14 +5776,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45931</v>
+        <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5849,14 +5849,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46085</v>
+        <v>46042</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5912,7 +5912,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5922,14 +5922,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45937</v>
+        <v>45194</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5985,7 +5985,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46091</v>
+        <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6014,13 +6014,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6063,7 +6058,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6077,10 +6072,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46092</v>
+        <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6092,13 +6087,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6141,7 +6131,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6155,10 +6145,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46092</v>
+        <v>46052</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6170,13 +6160,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6215,31 +6200,11 @@
         <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
-      <c r="Z59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6253,10 +6218,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46092</v>
+        <v>46052</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6268,13 +6233,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6317,7 +6277,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6327,14 +6287,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46092</v>
+        <v>45931</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,11 +6304,6 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -6395,7 +6350,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6405,14 +6360,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46092</v>
+        <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6424,13 +6379,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6473,7 +6423,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6487,10 +6437,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44995</v>
+        <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6503,7 +6453,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6546,7 +6496,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6560,10 +6510,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44757</v>
+        <v>46072</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6576,7 +6526,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6619,7 +6569,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6633,10 +6583,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44995</v>
+        <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6649,7 +6599,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6692,7 +6642,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6702,14 +6652,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44993</v>
+        <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6722,7 +6672,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6765,7 +6715,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6779,10 +6729,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44777</v>
+        <v>46091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6794,8 +6744,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6838,7 +6793,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6852,10 +6807,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45075</v>
+        <v>46092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6867,8 +6822,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6907,11 +6867,31 @@
         <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr"/>
+      <c r="Z68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6925,10 +6905,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46135</v>
+        <v>46092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6940,8 +6920,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6984,7 +6969,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6998,10 +6983,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45994</v>
+        <v>46092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7019,7 +7004,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7062,7 +7047,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7076,10 +7061,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45955</v>
+        <v>46092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7091,8 +7076,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7135,7 +7125,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7149,10 +7139,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45843</v>
+        <v>46092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7164,8 +7154,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7208,7 +7203,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7222,10 +7217,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45849</v>
+        <v>45307</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7237,13 +7232,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7286,7 +7276,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7300,10 +7290,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45854</v>
+        <v>45994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7321,7 +7311,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7364,7 +7354,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7378,10 +7368,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44518</v>
+        <v>46135</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7394,7 +7384,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7437,7 +7427,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7451,10 +7441,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45869</v>
+        <v>45075</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7467,7 +7457,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7510,7 +7500,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7524,10 +7514,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46140</v>
+        <v>45955</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7540,7 +7530,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7583,7 +7573,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7597,10 +7587,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46135</v>
+        <v>45849</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7612,8 +7602,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7656,7 +7651,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7670,10 +7665,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44518</v>
+        <v>45854</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7685,8 +7680,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>6.9</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7729,7 +7729,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45770</v>
+        <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7802,7 +7802,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45352</v>
+        <v>45843</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7831,13 +7831,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7880,7 +7875,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7894,10 +7889,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45112</v>
+        <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7909,13 +7904,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7958,7 +7948,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7972,10 +7962,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45306</v>
+        <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7987,13 +7977,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8036,7 +8021,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8050,10 +8035,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46167</v>
+        <v>45869</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8066,7 +8051,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8109,7 +8094,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8119,14 +8104,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45194</v>
+        <v>44995</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8139,7 +8124,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8182,7 +8167,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8192,14 +8177,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44673</v>
+        <v>46167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8212,7 +8197,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8255,7 +8240,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8269,10 +8254,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45112</v>
+        <v>44757</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8284,13 +8269,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8333,7 +8313,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8347,10 +8327,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45223</v>
+        <v>44777</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8363,7 +8343,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>16.3</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8406,7 +8386,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8420,10 +8400,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45642</v>
+        <v>45223</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8436,7 +8416,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>16.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8479,7 +8459,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8493,10 +8473,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45414</v>
+        <v>44518</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8509,7 +8489,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8552,7 +8532,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8566,10 +8546,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46255</v>
+        <v>44846</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8581,13 +8561,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8630,7 +8605,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8644,10 +8619,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45307</v>
+        <v>46261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8659,8 +8634,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8703,7 +8683,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8717,10 +8697,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46261</v>
+        <v>45675</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8732,13 +8712,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8781,7 +8756,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8795,10 +8770,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45675</v>
+        <v>44959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8811,7 +8786,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8871,7 +8846,7 @@
         <v>46193</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8927,7 +8902,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8944,7 +8919,7 @@
         <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8962,7 +8937,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9005,7 +8980,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9022,7 +8997,7 @@
         <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9040,7 +9015,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9083,7 +9058,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9097,10 +9072,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44993</v>
+        <v>46275</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9112,8 +9087,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9156,7 +9136,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9170,10 +9150,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45187</v>
+        <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9185,13 +9165,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9234,7 +9209,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9248,10 +9223,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46275</v>
+        <v>45112</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9269,7 +9244,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9312,7 +9287,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9326,10 +9301,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44791</v>
+        <v>45187</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9343,11 +9318,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9390,7 +9365,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 39978-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9404,10 +9379,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44735</v>
+        <v>46293</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9419,8 +9394,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9463,7 +9443,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9477,10 +9457,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45675</v>
+        <v>45352</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9492,8 +9472,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9536,7 +9521,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 39978-2026</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9550,10 +9535,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46293</v>
+        <v>46255</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9571,7 +9556,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9614,7 +9599,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9628,10 +9613,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44959</v>
+        <v>45770</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9644,7 +9629,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9687,7 +9672,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9701,10 +9686,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44846</v>
+        <v>45390</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9716,8 +9701,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9760,7 +9750,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9774,10 +9764,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45034</v>
+        <v>45306</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9789,8 +9779,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9833,7 +9828,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9847,10 +9842,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45300</v>
+        <v>45112</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9862,8 +9857,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9923,7 +9923,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46127</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44959</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>46029</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>46071</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45675</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45414</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>46042</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45194</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46052</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46052</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45931</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>46072</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>46091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>46092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>46092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>46092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45307</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46135</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45075</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45955</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45849</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45854</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45843</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45869</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44995</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>46167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44757</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44777</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45223</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44518</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44846</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>46261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45675</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>46193</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>46275</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45112</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45187</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>46293</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45352</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>46255</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45770</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45390</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45306</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>45112</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>46127</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44959</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>46029</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>46071</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44791</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45034</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45675</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45414</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44995</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>46042</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45194</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>45922</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>46052</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>46052</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45931</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>45937</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>46072</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>46091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>46092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>46092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>46092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>46092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45307</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45994</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46135</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45075</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45955</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45849</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45854</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45843</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>46135</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45869</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44995</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>46167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44757</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44777</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45223</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44518</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44846</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>46261</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45675</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44959</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>46193</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>46275</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>46275</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>44993</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45112</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45187</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>46293</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45352</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>46255</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45770</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>45390</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45306</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>45112</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46092</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45715</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44735</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61768-2025</t>
+          <t>A 34859-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46002</v>
+        <v>45849</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2358,17 +2358,22 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2383,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2399,372 +2404,367 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>Mörk husmossa
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 13004-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>Gullpudra
 Kamjordstjärna</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 13004-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Kransmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 34859-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45849</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Mörk husmossa
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
         <v>45679</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44959</v>
+        <v>46043</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2943,46 +2943,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2996,10 +3000,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46029</v>
+        <v>46071</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3011,18 +3015,23 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -3036,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3052,46 +3061,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46043</v>
+        <v>45726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3121,20 +3126,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -3145,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3157,50 +3162,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3214,10 +3215,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46071</v>
+        <v>46092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3231,20 +3232,20 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3259,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3271,39 +3272,43 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
@@ -3327,7 +3332,7 @@
         <v>46092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3438,10 +3443,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,13 +3458,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3499,46 +3499,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46094</v>
+        <v>45133</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3567,8 +3567,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3604,50 +3609,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3666,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45133</v>
+        <v>44959</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,26 +3681,21 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3706,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3722,46 +3722,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3775,10 +3771,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45726</v>
+        <v>46029</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3791,10 +3787,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3803,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3815,10 +3811,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3831,35 +3827,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
         <v>44497</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45309</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44655</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44847</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>44536</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44690</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44503</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44548</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44791</v>
+        <v>45390</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5135,11 +5135,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45034</v>
+        <v>46042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5255,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>46043</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45675</v>
+        <v>46052</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45300</v>
+        <v>46052</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45414</v>
+        <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46029</v>
+        <v>45849</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5576,8 +5576,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5620,7 +5625,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5634,10 +5639,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44995</v>
+        <v>45854</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5649,8 +5654,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5693,7 +5703,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5707,10 +5717,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44993</v>
+        <v>44757</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5723,7 +5733,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5766,7 +5776,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5780,10 +5790,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46043</v>
+        <v>44995</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5796,7 +5806,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5839,7 +5849,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5853,10 +5863,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46042</v>
+        <v>44993</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5869,7 +5879,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5912,7 +5922,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5922,14 +5932,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45194</v>
+        <v>45869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5942,7 +5952,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5985,7 +5995,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5999,10 +6009,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45439</v>
+        <v>45922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6015,7 +6025,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6058,7 +6068,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6072,10 +6082,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45922</v>
+        <v>44777</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6088,7 +6098,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6131,7 +6141,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6141,14 +6151,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46052</v>
+        <v>45931</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6161,7 +6171,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6204,7 +6214,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6218,10 +6228,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46052</v>
+        <v>45075</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6234,7 +6244,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6277,7 +6287,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6287,14 +6297,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45931</v>
+        <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6307,7 +6317,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6350,7 +6360,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6360,14 +6370,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44673</v>
+        <v>46072</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6380,7 +6390,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6423,7 +6433,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6433,14 +6443,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45937</v>
+        <v>46085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6453,7 +6463,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6496,7 +6506,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6510,10 +6520,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46072</v>
+        <v>46091</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6525,8 +6535,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6569,7 +6584,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6583,10 +6598,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45642</v>
+        <v>46092</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6598,8 +6613,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6642,7 +6662,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6652,14 +6672,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6671,8 +6691,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6711,11 +6736,31 @@
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr"/>
+      <c r="Z66">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA66">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB66">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC66">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD66">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6729,10 +6774,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6750,7 +6795,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6793,7 +6838,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6810,7 +6855,7 @@
         <v>46092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6828,7 +6873,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6867,31 +6912,11 @@
         <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr"/>
-      <c r="Z68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6908,7 +6933,7 @@
         <v>46092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6926,7 +6951,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6969,7 +6994,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6983,10 +7008,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46092</v>
+        <v>44518</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6998,13 +7023,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7047,7 +7067,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7061,10 +7081,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46092</v>
+        <v>45994</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7082,7 +7102,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7125,7 +7145,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7139,10 +7159,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46092</v>
+        <v>46135</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7154,13 +7174,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7203,7 +7218,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7217,10 +7232,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45307</v>
+        <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7233,7 +7248,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7276,7 +7291,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7290,10 +7305,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45994</v>
+        <v>46029</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7305,13 +7320,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7354,7 +7364,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7368,10 +7378,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46135</v>
+        <v>45770</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7384,7 +7394,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7427,7 +7437,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7441,10 +7451,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45075</v>
+        <v>45352</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7456,8 +7466,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7517,7 +7532,7 @@
         <v>45955</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7573,7 +7588,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7587,10 +7602,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45849</v>
+        <v>45112</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7608,7 +7623,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7651,7 +7666,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7665,10 +7680,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45854</v>
+        <v>45843</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7680,13 +7695,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7729,7 +7739,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7743,10 +7753,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44518</v>
+        <v>45306</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7758,8 +7768,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>6.9</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7802,7 +7817,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7816,10 +7831,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45843</v>
+        <v>46140</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7832,7 +7847,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7875,7 +7890,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7889,10 +7904,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46140</v>
+        <v>46135</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7905,7 +7920,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7948,7 +7963,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7962,10 +7977,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46135</v>
+        <v>46167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7978,7 +7993,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8021,7 +8036,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8031,14 +8046,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45869</v>
+        <v>45194</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8051,7 +8066,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8094,7 +8109,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8104,14 +8119,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44995</v>
+        <v>44673</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8124,7 +8139,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8167,7 +8182,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8181,10 +8196,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46167</v>
+        <v>45112</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8196,8 +8211,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8240,7 +8260,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8254,10 +8274,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44757</v>
+        <v>45223</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8270,7 +8290,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.7</v>
+        <v>16.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8313,7 +8333,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8327,10 +8347,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44777</v>
+        <v>45642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8343,7 +8363,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8386,7 +8406,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8400,10 +8420,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45223</v>
+        <v>45414</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8416,7 +8436,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>16.3</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8459,7 +8479,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8473,10 +8493,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44518</v>
+        <v>45307</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8489,7 +8509,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8532,7 +8552,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8546,10 +8566,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44846</v>
+        <v>45675</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8562,7 +8582,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8605,7 +8625,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8619,10 +8639,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46261</v>
+        <v>44993</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8634,13 +8654,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8683,7 +8698,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8697,10 +8712,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45675</v>
+        <v>45187</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8712,8 +8727,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8756,7 +8776,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8770,10 +8790,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44959</v>
+        <v>46261</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8785,8 +8805,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8829,7 +8854,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8839,14 +8864,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46193</v>
+        <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8858,8 +8883,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8902,7 +8932,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8912,14 +8942,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46275</v>
+        <v>46193</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8931,13 +8961,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8997,7 +9022,7 @@
         <v>46275</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9075,7 +9100,7 @@
         <v>46275</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9136,7 +9161,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9150,10 +9175,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44993</v>
+        <v>44735</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9166,7 +9191,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9209,7 +9234,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9223,10 +9248,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45112</v>
+        <v>46275</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9244,7 +9269,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9287,7 +9312,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9301,10 +9326,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45187</v>
+        <v>45675</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9316,13 +9341,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9365,7 +9385,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39978-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9379,10 +9399,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46293</v>
+        <v>44959</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9394,13 +9414,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9443,7 +9458,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9457,10 +9472,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45352</v>
+        <v>44846</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9472,13 +9487,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9521,7 +9531,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9535,10 +9545,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46255</v>
+        <v>45034</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9550,13 +9560,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9599,7 +9604,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 39978-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9613,10 +9618,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45770</v>
+        <v>46293</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9628,8 +9633,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9672,7 +9682,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9686,10 +9696,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45390</v>
+        <v>45300</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9701,13 +9711,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9750,7 +9755,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 34604-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9764,10 +9769,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45306</v>
+        <v>46255</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9785,7 +9790,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9828,7 +9833,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9842,10 +9847,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45112</v>
+        <v>45439</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9857,13 +9862,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9923,7 +9923,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1760,24 +1760,24 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S 3400-2025</t>
+          <t>A 35395-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45994</v>
+        <v>46261</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1795,19 +1795,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>158.5</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1819,21 +1819,136 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
       </c>
       <c r="T11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Spinnfingersvamp
+Ullticka
+Blodticka
+Vedticka
+Kransmossa
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 35395-2026 artfynd.xlsx", "A 35395-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 35395-2026 karta.png", "A 35395-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 35395-2026 georefererad karta.tif", "A 35395-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 35395-2026 FSC-klagomål.docx", "A 35395-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 35395-2026 FSC-klagomål mail.docx", "A 35395-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 35395-2026 tillsynsbegäran.docx", "A 35395-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 35395-2026 tillsynsbegäran mail.docx", "A 35395-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 3400-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Mindre bastardsvärmare
 Grönpyrola
@@ -1843,116 +1958,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/S 3400-2025 artfynd.xlsx", "S 3400-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/S 3400-2025 karta.png", "S 3400-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/S 3400-2025 georefererad karta.tif", "S 3400-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/S 3400-2025 FSC-klagomål.docx", "S 3400-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/S 3400-2025 FSC-klagomål mail.docx", "S 3400-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/S 3400-2025 tillsynsbegäran.docx", "S 3400-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/S 3400-2025 tillsynsbegäran mail.docx", "S 3400-2025")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/S 3400-2025 prioriterade fågelarter.docx", "S 3400-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 12958-2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46092</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>3.8</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>5</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Tallkötticka
 Ullticka
@@ -1961,111 +2076,111 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 17101-2023</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45034</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>4.2</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>5</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>4</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -2074,111 +2189,229 @@
 Trådticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 34604-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Blåsippa
+Kransmossa
+Tjäder
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34604-2026 artfynd.xlsx", "A 34604-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34604-2026 karta.png", "A 34604-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34604-2026 georefererad karta.tif", "A 34604-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34604-2026 FSC-klagomål.docx", "A 34604-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34604-2026 FSC-klagomål mail.docx", "A 34604-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34604-2026 tillsynsbegäran.docx", "A 34604-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34604-2026 tillsynsbegäran mail.docx", "A 34604-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 34604-2026 prioriterade fågelarter.docx", "A 34604-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 9553-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>3.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>4</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>5</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Gulvit blekspik
 Veckticka
@@ -2186,917 +2419,698 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9553-2025 artfynd.xlsx", "A 9553-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9553-2025 karta.png", "A 9553-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9553-2025 georefererad karta.tif", "A 9553-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9553-2025 FSC-klagomål.docx", "A 9553-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9553-2025 FSC-klagomål mail.docx", "A 9553-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9553-2025 tillsynsbegäran.docx", "A 9553-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9553-2025 tillsynsbegäran mail.docx", "A 9553-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 26239-2022</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>44735</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>4.4</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>4</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Järnsparv
 Grönsiska</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 26239-2022 artfynd.xlsx", "A 26239-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 26239-2022 karta.png", "A 26239-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 26239-2022 georefererad karta.tif", "A 26239-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 26239-2022 FSC-klagomål.docx", "A 26239-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 26239-2022 FSC-klagomål mail.docx", "A 26239-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 26239-2022 tillsynsbegäran.docx", "A 26239-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 26239-2022 tillsynsbegäran mail.docx", "A 26239-2022")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 26239-2022 prioriterade fågelarter.docx", "A 26239-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 13004-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 34859-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45849</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Holmen skog AB</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I19" t="n">
         <v>6.1</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Mörk husmossa
 Rostfläck</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 13004-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="D20" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U20" t="n">
         <v>7</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Kransmossa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 61768-2025</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46002</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>3</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Kamjordstjärna</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>S 194-2025</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45679</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T22" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Grovticka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/S 194-2025 artfynd.xlsx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/S 194-2025 karta.png", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/S 194-2025 georefererad karta.tif", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/S 194-2025 FSC-klagomål.docx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/S 194-2025 FSC-klagomål mail.docx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/S 194-2025 tillsynsbegäran.docx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/S 194-2025 tillsynsbegäran mail.docx", "S 194-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 3836-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46043</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 9561-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46071</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Svartöra</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3110,10 +3124,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45726</v>
+        <v>46029</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3126,10 +3140,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3138,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3150,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3166,42 +3180,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3215,10 +3233,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46092</v>
+        <v>46043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3230,13 +3248,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3276,46 +3289,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,10 +3342,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46092</v>
+        <v>46071</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3346,23 +3359,23 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3377,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3386,50 +3399,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3443,10 +3452,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3458,8 +3467,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3471,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3483,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3499,46 +3513,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3552,10 +3566,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45133</v>
+        <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3573,7 +3587,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3609,50 +3623,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3666,10 +3680,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44959</v>
+        <v>46094</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3682,10 +3696,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3694,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3706,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3718,46 +3732,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 666-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3771,10 +3789,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46029</v>
+        <v>44959</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3787,10 +3805,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3799,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3811,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3827,46 +3845,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3880,10 +3894,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44497</v>
+        <v>45133</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3895,14 +3909,19 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3932,46 +3951,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3985,10 +4008,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44518</v>
+        <v>46275</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4000,8 +4023,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4013,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -4025,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4041,42 +4069,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 37356-2026 artfynd.xlsx", "A 37356-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 37356-2026 karta.png", "A 37356-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 37356-2026 georefererad karta.tif", "A 37356-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 37356-2026 FSC-klagomål.docx", "A 37356-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 37356-2026 FSC-klagomål mail.docx", "A 37356-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 37356-2026 tillsynsbegäran.docx", "A 37356-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 37356-2026 tillsynsbegäran mail.docx", "A 37356-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2171-2024</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4090,10 +4118,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45309</v>
+        <v>45726</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,16 +4133,11 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -4123,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4135,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4147,63 +4170,63 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S 1786-2022</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44655</v>
+        <v>44497</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,22 +4238,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4245,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4257,46 +4275,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/S 1786-2022 artfynd.xlsx", "S 1786-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/S 1786-2022 karta.png", "S 1786-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/S 1786-2022 georefererad karta.tif", "S 1786-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/S 1786-2022 FSC-klagomål.docx", "S 1786-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/S 1786-2022 FSC-klagomål mail.docx", "S 1786-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/S 1786-2022 tillsynsbegäran.docx", "S 1786-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/S 1786-2022 tillsynsbegäran mail.docx", "S 1786-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 66298-2021</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4313,7 +4331,7 @@
         <v>44518</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4326,7 +4344,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4338,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4350,26 +4368,58 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 46149-2022</t>
+          <t>A 2171-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4383,10 +4433,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44847</v>
+        <v>45309</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4398,11 +4448,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4429,37 +4484,69 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16775-2022</t>
+          <t>S 1786-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44673</v>
+        <v>44655</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4471,8 +4558,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4481,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4496,26 +4588,58 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/S 1786-2022 artfynd.xlsx", "S 1786-2022")</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/S 1786-2022 karta.png", "S 1786-2022")</f>
+        <v/>
+      </c>
+      <c r="Y36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/S 1786-2022 georefererad karta.tif", "S 1786-2022")</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/S 1786-2022 FSC-klagomål.docx", "S 1786-2022")</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/S 1786-2022 FSC-klagomål mail.docx", "S 1786-2022")</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/S 1786-2022 tillsynsbegäran.docx", "S 1786-2022")</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/S 1786-2022 tillsynsbegäran mail.docx", "S 1786-2022")</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62451-2021</t>
+          <t>A 66298-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4529,10 +4653,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44509</v>
+        <v>44518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4545,7 +4669,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4588,7 +4712,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64044-2021</t>
+          <t>A 46149-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4602,10 +4726,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44510</v>
+        <v>44847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4618,7 +4742,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4661,7 +4785,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 70275-2021</t>
+          <t>A 16775-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4671,14 +4795,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44536</v>
+        <v>44673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4690,13 +4814,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4739,7 +4858,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 66256-2021</t>
+          <t>A 62451-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4753,10 +4872,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44518</v>
+        <v>44509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4769,7 +4888,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4812,7 +4931,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18820-2022</t>
+          <t>A 64044-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4826,10 +4945,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44690</v>
+        <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4842,7 +4961,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4885,7 +5004,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62441-2021</t>
+          <t>A 70275-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4899,10 +5018,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44503</v>
+        <v>44536</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4914,8 +5033,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4958,7 +5082,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 72966-2021</t>
+          <t>A 66256-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4972,10 +5096,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44548</v>
+        <v>44518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +5112,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5031,7 +5155,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 18820-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5045,10 +5169,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44548</v>
+        <v>44690</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5061,7 +5185,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5104,7 +5228,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 62441-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5118,10 +5242,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45390</v>
+        <v>44503</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5133,13 +5257,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5182,7 +5301,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 72966-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5196,10 +5315,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46042</v>
+        <v>44548</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5212,7 +5331,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5255,7 +5374,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5269,10 +5388,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46043</v>
+        <v>44548</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5285,7 +5404,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5328,7 +5447,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5342,10 +5461,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46052</v>
+        <v>44791</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5357,8 +5476,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5401,7 +5525,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5415,10 +5539,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46052</v>
+        <v>45034</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5431,7 +5555,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5474,7 +5598,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5488,10 +5612,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44995</v>
+        <v>44735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5628,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5547,7 +5671,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5561,10 +5685,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45849</v>
+        <v>45675</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5576,13 +5700,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5625,7 +5744,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5639,10 +5758,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45854</v>
+        <v>45414</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5654,13 +5773,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5703,7 +5817,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5717,10 +5831,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44757</v>
+        <v>44995</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5733,7 +5847,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5776,7 +5890,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5786,14 +5900,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44995</v>
+        <v>45194</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5806,7 +5920,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5866,7 +5980,7 @@
         <v>44993</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5922,7 +6036,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5936,10 +6050,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45869</v>
+        <v>46029</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5995,7 +6109,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6009,10 +6123,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45922</v>
+        <v>45439</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6025,7 +6139,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6068,7 +6182,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6082,10 +6196,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44777</v>
+        <v>46043</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6098,7 +6212,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6141,7 +6255,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6151,14 +6265,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45931</v>
+        <v>46042</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6171,7 +6285,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6214,7 +6328,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6224,14 +6338,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45075</v>
+        <v>44673</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6244,7 +6358,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6287,7 +6401,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6301,10 +6415,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45937</v>
+        <v>46052</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6317,7 +6431,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6360,7 +6474,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6374,10 +6488,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46072</v>
+        <v>46052</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6390,7 +6504,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6433,7 +6547,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6443,14 +6557,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46085</v>
+        <v>46072</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6463,7 +6577,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6506,7 +6620,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6520,10 +6634,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46091</v>
+        <v>45642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6535,13 +6649,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6584,7 +6693,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6598,10 +6707,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46092</v>
+        <v>45922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6613,13 +6722,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6662,7 +6766,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6672,14 +6776,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6691,13 +6795,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6736,31 +6835,11 @@
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr"/>
-      <c r="Z66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD66">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6774,10 +6853,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6795,7 +6874,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6838,7 +6917,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6855,7 +6934,7 @@
         <v>46092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6873,7 +6952,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6912,11 +6991,31 @@
         <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr"/>
+      <c r="Z68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD68">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6933,7 +7032,7 @@
         <v>46092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6951,7 +7050,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6994,7 +7093,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7008,10 +7107,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7023,8 +7122,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7067,7 +7171,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7081,10 +7185,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45994</v>
+        <v>46092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7102,7 +7206,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7145,7 +7249,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7159,10 +7263,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46135</v>
+        <v>46092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7174,8 +7278,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7218,7 +7327,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7228,14 +7337,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44518</v>
+        <v>45931</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7248,7 +7357,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7291,7 +7400,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7305,10 +7414,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46029</v>
+        <v>45937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7321,7 +7430,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7364,7 +7473,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7378,10 +7487,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45770</v>
+        <v>45307</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7394,7 +7503,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7437,7 +7546,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7451,10 +7560,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45352</v>
+        <v>45849</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7472,7 +7581,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7515,7 +7624,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7529,10 +7638,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45955</v>
+        <v>45854</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7544,8 +7653,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7588,7 +7702,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7602,10 +7716,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45112</v>
+        <v>45869</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7617,13 +7731,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7666,7 +7775,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7680,10 +7789,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45843</v>
+        <v>46135</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7696,7 +7805,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7739,7 +7848,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7753,10 +7862,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45306</v>
+        <v>45955</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7768,13 +7877,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7817,7 +7921,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7831,10 +7935,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46140</v>
+        <v>45994</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7846,8 +7950,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7890,7 +7999,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7904,10 +8013,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46135</v>
+        <v>45843</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7920,7 +8029,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7963,7 +8072,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7977,10 +8086,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46167</v>
+        <v>46140</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7993,7 +8102,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8036,7 +8145,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8046,14 +8155,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45194</v>
+        <v>46135</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8066,7 +8175,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8109,7 +8218,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8119,14 +8228,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44673</v>
+        <v>45075</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8139,7 +8248,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8182,7 +8291,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8196,10 +8305,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45112</v>
+        <v>46167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8211,13 +8320,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8260,7 +8364,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8274,10 +8378,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45223</v>
+        <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8290,7 +8394,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>16.3</v>
+        <v>6.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8333,7 +8437,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8347,10 +8451,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45642</v>
+        <v>44995</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8363,7 +8467,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8406,7 +8510,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8420,10 +8524,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45414</v>
+        <v>44757</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8436,7 +8540,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8479,7 +8583,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8493,10 +8597,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45307</v>
+        <v>44777</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8509,7 +8613,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8552,7 +8656,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8562,14 +8666,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45675</v>
+        <v>46193</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8582,7 +8686,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>7.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8625,7 +8729,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8639,10 +8743,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44993</v>
+        <v>45223</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8655,7 +8759,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>16.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8698,7 +8802,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8712,10 +8816,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45187</v>
+        <v>46275</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8729,11 +8833,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8776,7 +8880,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35395-2026</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8790,10 +8894,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8811,7 +8915,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8854,7 +8958,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8868,10 +8972,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44791</v>
+        <v>44518</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8883,13 +8987,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8932,7 +9031,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8942,14 +9041,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46193</v>
+        <v>44846</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8962,7 +9061,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9005,7 +9104,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9019,10 +9118,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46275</v>
+        <v>45675</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9034,13 +9133,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9083,7 +9177,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9097,10 +9191,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46275</v>
+        <v>44959</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9112,13 +9206,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9161,7 +9250,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 39978-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9175,10 +9264,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44735</v>
+        <v>46293</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9190,8 +9279,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9234,7 +9328,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9248,10 +9342,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46275</v>
+        <v>44993</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9263,13 +9357,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9312,7 +9401,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9326,10 +9415,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45675</v>
+        <v>45112</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9341,8 +9430,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9385,7 +9479,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9399,10 +9493,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44959</v>
+        <v>45187</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9414,8 +9508,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9458,7 +9557,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9472,10 +9571,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44846</v>
+        <v>45352</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9487,8 +9586,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9531,7 +9635,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9545,10 +9649,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45034</v>
+        <v>45770</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9561,7 +9665,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9604,7 +9708,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 39978-2026</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9618,10 +9722,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46293</v>
+        <v>45390</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9639,7 +9743,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9682,7 +9786,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9696,10 +9800,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45300</v>
+        <v>45306</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9711,8 +9815,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9755,7 +9864,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 34604-2026</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9769,10 +9878,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46255</v>
+        <v>45112</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9790,7 +9899,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9833,7 +9942,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9847,10 +9956,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45439</v>
+        <v>45300</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9863,7 +9972,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9923,7 +10032,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         <v>39</v>
       </c>
       <c r="T2" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="U2" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>46261</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45994</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12958-2026</t>
+          <t>A 17101-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46092</v>
+        <v>45034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2023,22 +2023,17 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2053,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2065,9 +2060,127 @@
         <v>5</v>
       </c>
       <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Ullticka
+Grön sköldmossa
+Trådticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 12958-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>5</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Tallkötticka
 Ullticka
@@ -2076,149 +2189,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 17101-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45034</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Ullticka
-Grön sköldmossa
-Trådticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
         <v/>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>46255</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
         <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44735</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13004-2026</t>
+          <t>A 34859-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46092</v>
+        <v>45849</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,19 +2597,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>6.1</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2633,395 +2633,395 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Mörk husmossa
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 13004-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 34859-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>45849</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="D21" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Mörk husmossa
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 34859-2025 artfynd.xlsx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 34859-2025 karta.png", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 34859-2025 georefererad karta.tif", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 34859-2025 FSC-klagomål.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 34859-2025 FSC-klagomål mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 34859-2025 tillsynsbegäran.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 34859-2025 tillsynsbegäran mail.docx", "A 34859-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 18576-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>7</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Kransmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 61768-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Kamjordstjärna</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 61768-2025 artfynd.xlsx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 61768-2025 karta.png", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 61768-2025 georefererad karta.tif", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 61768-2025 FSC-klagomål.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 61768-2025 FSC-klagomål mail.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 61768-2025 tillsynsbegäran.docx", "A 61768-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 61768-2025 tillsynsbegäran mail.docx", "A 61768-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S 194-2025</t>
+          <t>A 37356-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45679</v>
+        <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,14 +3033,19 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -3067,159 +3072,160 @@
         <v>2</v>
       </c>
       <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 37356-2026 artfynd.xlsx", "A 37356-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 37356-2026 karta.png", "A 37356-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 37356-2026 georefererad karta.tif", "A 37356-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 37356-2026 FSC-klagomål.docx", "A 37356-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 37356-2026 FSC-klagomål mail.docx", "A 37356-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 37356-2026 tillsynsbegäran.docx", "A 37356-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 37356-2026 tillsynsbegäran mail.docx", "A 37356-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 37356-2026 prioriterade fågelarter.docx", "A 37356-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S 194-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45679</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Grovticka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/S 194-2025 artfynd.xlsx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/S 194-2025 karta.png", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/S 194-2025 georefererad karta.tif", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/S 194-2025 FSC-klagomål.docx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/S 194-2025 FSC-klagomål mail.docx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/S 194-2025 tillsynsbegäran.docx", "S 194-2025")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/S 194-2025 tillsynsbegäran mail.docx", "S 194-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 666-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46029</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3836-2026</t>
+          <t>A 33770-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3233,10 +3239,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46043</v>
+        <v>45133</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3248,8 +3254,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3285,50 +3296,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9561-2026</t>
+          <t>A 2171-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3342,10 +3353,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46071</v>
+        <v>45309</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,20 +3370,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3387,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3399,46 +3410,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13002-2026</t>
+          <t>A 60885-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3452,10 +3463,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>44497</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3467,25 +3478,20 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3497,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3513,46 +3519,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12991-2026</t>
+          <t>A 5402-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3566,10 +3568,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46092</v>
+        <v>44959</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3581,16 +3583,11 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3599,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3611,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3623,50 +3620,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Askfingersvamp</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13380-2026</t>
+          <t>A 666-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3680,10 +3673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46094</v>
+        <v>46029</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3696,7 +3689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3732,50 +3725,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 666-2026 artfynd.xlsx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 666-2026 karta.png", "A 666-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 666-2026 georefererad karta.tif", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 666-2026 FSC-klagomål.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 666-2026 FSC-klagomål mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 666-2026 tillsynsbegäran.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 666-2026 tillsynsbegäran mail.docx", "A 666-2026")</f>
         <v/>
       </c>
       <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 666-2026 prioriterade fågelarter.docx", "A 666-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5402-2023</t>
+          <t>A 11405-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3789,10 +3782,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44959</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3805,7 +3798,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3845,42 +3838,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Askfingersvamp</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 5402-2023 artfynd.xlsx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 5402-2023 karta.png", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 5402-2023 georefererad karta.tif", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 5402-2023 FSC-klagomål.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 5402-2023 FSC-klagomål mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 5402-2023 tillsynsbegäran.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 5402-2023 tillsynsbegäran mail.docx", "A 5402-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33770-2023</t>
+          <t>A 66305-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3894,10 +3887,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45133</v>
+        <v>44518</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3909,16 +3902,11 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3927,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3939,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3951,50 +3939,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 33770-2023 artfynd.xlsx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 33770-2023 karta.png", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 33770-2023 georefererad karta.tif", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 33770-2023 FSC-klagomål.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 33770-2023 FSC-klagomål mail.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 33770-2023 tillsynsbegäran.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 33770-2023 tillsynsbegäran mail.docx", "A 33770-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 33770-2023 prioriterade fågelarter.docx", "A 33770-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37356-2026</t>
+          <t>A 3836-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4008,10 +3992,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46275</v>
+        <v>46043</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4023,16 +4007,11 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -4069,42 +4048,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 37356-2026 artfynd.xlsx", "A 37356-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 3836-2026 artfynd.xlsx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 37356-2026 karta.png", "A 37356-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 3836-2026 karta.png", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 37356-2026 georefererad karta.tif", "A 37356-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 3836-2026 georefererad karta.tif", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 37356-2026 FSC-klagomål.docx", "A 37356-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 3836-2026 FSC-klagomål.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 37356-2026 FSC-klagomål mail.docx", "A 37356-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 3836-2026 FSC-klagomål mail.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 37356-2026 tillsynsbegäran.docx", "A 37356-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 3836-2026 tillsynsbegäran.docx", "A 3836-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 37356-2026 tillsynsbegäran mail.docx", "A 37356-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 3836-2026 tillsynsbegäran mail.docx", "A 3836-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 3836-2026 prioriterade fågelarter.docx", "A 3836-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11405-2025</t>
+          <t>A 9561-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4118,10 +4101,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45726</v>
+        <v>46071</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4133,8 +4116,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4143,10 +4131,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4161,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4174,42 +4162,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 11405-2025 artfynd.xlsx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 9561-2026 artfynd.xlsx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 11405-2025 karta.png", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 9561-2026 karta.png", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 11405-2025 georefererad karta.tif", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 9561-2026 georefererad karta.tif", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 11405-2025 FSC-klagomål.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 9561-2026 FSC-klagomål.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 11405-2025 FSC-klagomål mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 9561-2026 FSC-klagomål mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 11405-2025 tillsynsbegäran.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 9561-2026 tillsynsbegäran.docx", "A 9561-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 11405-2025 tillsynsbegäran mail.docx", "A 11405-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 9561-2026 tillsynsbegäran mail.docx", "A 9561-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60885-2021</t>
+          <t>A 12991-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4223,10 +4211,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44497</v>
+        <v>46092</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,14 +4226,19 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4279,42 +4272,46 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 60885-2021 artfynd.xlsx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12991-2026 artfynd.xlsx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 60885-2021 karta.png", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12991-2026 karta.png", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 60885-2021 georefererad karta.tif", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12991-2026 georefererad karta.tif", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 60885-2021 FSC-klagomål.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12991-2026 FSC-klagomål.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 60885-2021 FSC-klagomål mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12991-2026 FSC-klagomål mail.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 60885-2021 tillsynsbegäran.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12991-2026 tillsynsbegäran.docx", "A 12991-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 60885-2021 tillsynsbegäran mail.docx", "A 60885-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12991-2026 tillsynsbegäran mail.docx", "A 12991-2026")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12991-2026 prioriterade fågelarter.docx", "A 12991-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 66305-2021</t>
+          <t>A 13002-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4328,10 +4325,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,11 +4340,16 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -4384,42 +4386,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 66305-2021 artfynd.xlsx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13002-2026 artfynd.xlsx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 66305-2021 karta.png", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13002-2026 karta.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 66305-2021 georefererad karta.tif", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13002-2026 georefererad karta.tif", "A 13002-2026")</f>
+        <v/>
+      </c>
+      <c r="Z34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13002-2026 karta knärot.png", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 66305-2021 FSC-klagomål.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13002-2026 FSC-klagomål.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 66305-2021 FSC-klagomål mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13002-2026 FSC-klagomål mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 66305-2021 tillsynsbegäran.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13002-2026 tillsynsbegäran.docx", "A 13002-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 66305-2021 tillsynsbegäran mail.docx", "A 66305-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13002-2026 tillsynsbegäran mail.docx", "A 13002-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2171-2024</t>
+          <t>A 13380-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4433,10 +4439,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45309</v>
+        <v>46094</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4448,13 +4454,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4494,35 +4495,39 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 2171-2024 artfynd.xlsx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13380-2026 artfynd.xlsx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 2171-2024 karta.png", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13380-2026 karta.png", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 2171-2024 georefererad karta.tif", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13380-2026 georefererad karta.tif", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 2171-2024 FSC-klagomål.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13380-2026 FSC-klagomål.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 2171-2024 FSC-klagomål mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13380-2026 FSC-klagomål mail.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 2171-2024 tillsynsbegäran.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13380-2026 tillsynsbegäran.docx", "A 13380-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 2171-2024 tillsynsbegäran mail.docx", "A 2171-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13380-2026 tillsynsbegäran mail.docx", "A 13380-2026")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13380-2026 prioriterade fågelarter.docx", "A 13380-2026")</f>
         <v/>
       </c>
     </row>
@@ -4546,7 +4551,7 @@
         <v>44655</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4656,7 +4661,7 @@
         <v>44518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4729,7 +4734,7 @@
         <v>44847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4802,7 +4807,7 @@
         <v>44673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4875,7 +4880,7 @@
         <v>44509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4948,7 +4953,7 @@
         <v>44510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5021,7 +5026,7 @@
         <v>44536</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5099,7 +5104,7 @@
         <v>44518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5155,7 +5160,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18820-2022</t>
+          <t>A 72967-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5169,10 +5174,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44690</v>
+        <v>44548</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5185,7 +5190,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5228,7 +5233,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62441-2021</t>
+          <t>A 18820-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5242,10 +5247,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44503</v>
+        <v>44690</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5258,7 +5263,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5301,7 +5306,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 72966-2021</t>
+          <t>A 62441-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5315,10 +5320,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44548</v>
+        <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5331,7 +5336,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5374,7 +5379,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 72967-2021</t>
+          <t>A 72966-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5391,7 +5396,7 @@
         <v>44548</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5404,7 +5409,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5447,7 +5452,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34078-2022</t>
+          <t>A 66293-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44791</v>
+        <v>44518</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5476,13 +5481,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17091-2023</t>
+          <t>A 794-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45034</v>
+        <v>45300</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26182-2022</t>
+          <t>A 13697-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44735</v>
+        <v>45390</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5627,8 +5627,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5671,7 +5676,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2628-2025</t>
+          <t>A 66284-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5685,10 +5690,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45675</v>
+        <v>44518</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5701,7 +5706,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5744,7 +5749,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 17333-2024</t>
+          <t>A 20902-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5758,10 +5763,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45414</v>
+        <v>45439</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5774,7 +5779,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5817,7 +5822,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11841-2023</t>
+          <t>A 19676-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5831,10 +5836,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44995</v>
+        <v>45770</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5847,7 +5852,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5890,7 +5895,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45525-2023</t>
+          <t>A 8343-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5900,14 +5905,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45194</v>
+        <v>45352</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5919,8 +5924,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5963,7 +5973,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11450-2023</t>
+          <t>A 45453-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5977,10 +5987,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44993</v>
+        <v>45922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5993,7 +6003,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6036,7 +6046,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 662-2026</t>
+          <t>A 30627-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6050,10 +6060,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46029</v>
+        <v>45112</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6065,8 +6075,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6109,7 +6124,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20902-2024</t>
+          <t>A 1629-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6123,10 +6138,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45439</v>
+        <v>45306</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6138,8 +6153,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6182,7 +6202,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3824-2026</t>
+          <t>A 47803-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6192,14 +6212,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46043</v>
+        <v>45931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6212,7 +6232,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6255,7 +6275,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3375-2026</t>
+          <t>A 49090-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6269,10 +6289,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46042</v>
+        <v>45937</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6285,7 +6305,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6328,7 +6348,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16773-2022</t>
+          <t>A 34864-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6338,14 +6358,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44673</v>
+        <v>45849</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6357,8 +6377,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6401,7 +6426,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5908-2026</t>
+          <t>A 35318-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6415,10 +6440,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46052</v>
+        <v>45854</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6430,8 +6455,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6474,7 +6504,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5910-2026</t>
+          <t>A 36473-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6488,10 +6518,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46052</v>
+        <v>45869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6504,7 +6534,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6547,7 +6577,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9744-2026</t>
+          <t>A 11841-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6561,10 +6591,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46072</v>
+        <v>44995</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6577,7 +6607,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6620,7 +6650,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60018-2024</t>
+          <t>A 45525-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6630,14 +6660,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45642</v>
+        <v>45194</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6650,7 +6680,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6693,7 +6723,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45453-2025</t>
+          <t>A 52666-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6707,10 +6737,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45922</v>
+        <v>45955</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6723,7 +6753,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6766,7 +6796,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12027-2026</t>
+          <t>A 33974-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6776,14 +6806,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46085</v>
+        <v>45843</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6796,7 +6826,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6839,7 +6869,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12774-2026</t>
+          <t>A 30351-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6853,10 +6883,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46091</v>
+        <v>44757</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6868,13 +6898,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6917,7 +6942,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13011-2026</t>
+          <t>A 11847-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6931,10 +6956,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46092</v>
+        <v>44995</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6946,13 +6971,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6991,31 +7011,11 @@
         <v>0</v>
       </c>
       <c r="V68" s="2" t="inlineStr"/>
-      <c r="Z68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
-      <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
-        <v/>
-      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13013-2026</t>
+          <t>A 11450-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46092</v>
+        <v>44993</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7044,13 +7044,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7093,7 +7088,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13001-2026</t>
+          <t>A 31875-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7107,10 +7102,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46092</v>
+        <v>44777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7122,13 +7117,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7171,7 +7161,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13005-2026</t>
+          <t>A 20528-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7185,10 +7175,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46092</v>
+        <v>46140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7200,13 +7190,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7249,7 +7234,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13016-2026</t>
+          <t>A 16773-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7259,14 +7244,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46092</v>
+        <v>44673</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7278,13 +7263,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7327,7 +7307,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 47803-2025</t>
+          <t>A 30764-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7337,14 +7317,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45931</v>
+        <v>45112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7356,8 +7336,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7400,7 +7385,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49090-2025</t>
+          <t>A 19777-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7414,10 +7399,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45937</v>
+        <v>46135</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7430,7 +7415,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7473,7 +7458,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1791-2024</t>
+          <t>A 51849-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7487,10 +7472,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45307</v>
+        <v>45223</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7503,7 +7488,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>16.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7546,7 +7531,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34864-2025</t>
+          <t>A 60018-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7560,10 +7545,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45849</v>
+        <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7575,13 +7560,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7624,7 +7604,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35318-2025</t>
+          <t>A 60243-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7638,10 +7618,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45854</v>
+        <v>45994</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7659,7 +7639,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7702,7 +7682,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36473-2025</t>
+          <t>A 23239-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7716,10 +7696,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45869</v>
+        <v>45075</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7732,7 +7712,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7775,7 +7755,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19774-2026</t>
+          <t>A 17333-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7789,10 +7769,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46135</v>
+        <v>45414</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7805,7 +7785,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7848,7 +7828,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52666-2025</t>
+          <t>A 1791-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7862,10 +7842,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45955</v>
+        <v>45307</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7878,7 +7858,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7921,7 +7901,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60243-2025</t>
+          <t>A 23969-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7935,10 +7915,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45994</v>
+        <v>46167</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7950,13 +7930,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7999,7 +7974,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33974-2025</t>
+          <t>A 662-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8013,10 +7988,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45843</v>
+        <v>46029</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8029,7 +8004,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8072,7 +8047,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20528-2026</t>
+          <t>A 3375-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8086,10 +8061,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46140</v>
+        <v>46042</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8102,7 +8077,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8145,7 +8120,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19777-2026</t>
+          <t>A 3824-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8159,10 +8134,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46135</v>
+        <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8218,7 +8193,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 23239-2023</t>
+          <t>A 2628-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8232,10 +8207,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45075</v>
+        <v>45675</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8248,7 +8223,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8291,7 +8266,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23969-2026</t>
+          <t>A 5908-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8305,10 +8280,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46167</v>
+        <v>46052</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8321,7 +8296,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8364,7 +8339,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 66284-2021</t>
+          <t>A 5910-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8378,10 +8353,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44518</v>
+        <v>46052</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8394,7 +8369,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8437,7 +8412,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11847-2023</t>
+          <t>A 11452-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8451,10 +8426,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44995</v>
+        <v>44993</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8467,7 +8442,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8510,7 +8485,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30351-2022</t>
+          <t>A 43908-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8524,10 +8499,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44757</v>
+        <v>45187</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8539,8 +8514,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8583,7 +8563,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31875-2022</t>
+          <t>A 9744-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8597,10 +8577,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44777</v>
+        <v>46072</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8613,7 +8593,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8656,7 +8636,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28668-2026</t>
+          <t>A 12027-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8670,10 +8650,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46193</v>
+        <v>46085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8686,7 +8666,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8729,7 +8709,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51849-2023</t>
+          <t>A 34078-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8743,10 +8723,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45223</v>
+        <v>44791</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8758,8 +8738,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>16.3</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8802,7 +8787,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 37413-2026</t>
+          <t>A 12774-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8816,10 +8801,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46275</v>
+        <v>46091</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8837,7 +8822,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8880,7 +8865,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 37437-2026</t>
+          <t>A 13013-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8894,10 +8879,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46275</v>
+        <v>46092</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8915,7 +8900,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8958,7 +8943,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 66293-2021</t>
+          <t>A 13011-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8972,10 +8957,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44518</v>
+        <v>46092</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8987,8 +8972,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9027,11 +9017,31 @@
         <v>0</v>
       </c>
       <c r="V95" s="2" t="inlineStr"/>
+      <c r="Z95">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13011-2026 karta knärot.png", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AA95">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13011-2026 FSC-klagomål.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AB95">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13011-2026 FSC-klagomål mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AC95">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13011-2026 tillsynsbegäran.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
+      <c r="AD95">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13011-2026 tillsynsbegäran mail.docx", "A 13011-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 45916-2022</t>
+          <t>A 13016-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9045,10 +9055,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44846</v>
+        <v>46092</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9060,8 +9070,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9104,7 +9119,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2629-2025</t>
+          <t>A 13001-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9118,10 +9133,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45675</v>
+        <v>46092</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9133,8 +9148,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9177,7 +9197,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5320-2023</t>
+          <t>A 13005-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9191,10 +9211,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44959</v>
+        <v>46092</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9206,8 +9226,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9250,7 +9275,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39978-2026</t>
+          <t>A 26182-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9264,10 +9289,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46293</v>
+        <v>44735</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9279,13 +9304,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9328,7 +9348,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11452-2023</t>
+          <t>A 2629-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9342,10 +9362,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44993</v>
+        <v>45675</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9358,7 +9378,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9401,7 +9421,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30627-2023</t>
+          <t>A 5320-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9415,10 +9435,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45112</v>
+        <v>44959</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9430,13 +9450,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9479,7 +9494,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 43908-2023</t>
+          <t>A 19774-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9493,10 +9508,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45187</v>
+        <v>46135</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9508,13 +9523,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9557,7 +9567,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8343-2024</t>
+          <t>A 45916-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9571,10 +9581,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45352</v>
+        <v>44846</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,13 +9596,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9635,7 +9640,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19676-2025</t>
+          <t>A 17091-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9649,10 +9654,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45770</v>
+        <v>45034</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9665,7 +9670,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9708,7 +9713,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13697-2024</t>
+          <t>A 28668-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9718,14 +9723,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45390</v>
+        <v>46193</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9737,13 +9742,8 @@
           <t>KNIVSTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1629-2024</t>
+          <t>A 37413-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45306</v>
+        <v>46275</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9864,7 +9864,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30764-2023</t>
+          <t>A 37437-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45112</v>
+        <v>46275</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9942,7 +9942,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 794-2024</t>
+          <t>A 39978-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45300</v>
+        <v>46293</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9971,8 +9971,13 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10032,7 +10037,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/Översikt KNIVSTA.xlsx
+++ b/Översikt KNIVSTA.xlsx
@@ -601,7 +601,7 @@
         <v>44588</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>45693</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>45190</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45925</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>44971</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45213</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44712</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>46036</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44791</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>46261</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45994</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17101-2023</t>
+          <t>A 12958-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45034</v>
+        <v>46092</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2023,17 +2023,22 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2048,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2060,9 +2065,122 @@
         <v>5</v>
       </c>
       <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Tallkötticka
+Ullticka
+Blodticka
+Vågbandad barkbock
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 17101-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45034</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
         <v>4</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
@@ -2071,154 +2189,36 @@
 Trådticka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 17101-2023 artfynd.xlsx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 17101-2023 karta.png", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 17101-2023 georefererad karta.tif", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 17101-2023 FSC-klagomål.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 17101-2023 FSC-klagomål mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 17101-2023 tillsynsbegäran.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 17101-2023 tillsynsbegäran mail.docx", "A 17101-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 17101-2023 prioriterade fågelarter.docx", "A 17101-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 12958-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>UPPSALA LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KNIVSTA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>5</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tallkötticka
-Ullticka
-Blodticka
-Vågbandad barkbock
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 12958-2026 artfynd.xlsx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 12958-2026 karta.png", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 12958-2026 georefererad karta.tif", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 12958-2026 FSC-klagomål.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 12958-2026 FSC-klagomål mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 12958-2026 tillsynsbegäran.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 12958-2026 tillsynsbegäran mail.docx", "A 12958-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 12958-2026 prioriterade fågelarter.docx", "A 12958-2026")</f>
         <v/>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>46255</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44735</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45849</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 61768-2025</t>
+          <t>A 13004-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46002</v>
+        <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2702,20 +2702,25 @@
           <t>KNIVSTA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2730,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>2</v>
@@ -2739,265 +2744,260 @@
         <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 13004-2026 artfynd.xlsx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 13004-2026 karta.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 13004-2026 georefererad karta.tif", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/knärot/A 13004-2026 karta knärot.png", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 13004-2026 FSC-klagomål.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 13004-2026 FSC-klagomål mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 13004-2026 tillsynsbegäran.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 13004-2026 tillsynsbegäran mail.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/fåglar/A 13004-2026 prioriterade fågelarter.docx", "A 13004-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 18576-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KNIVSTA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Kransmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/artfynd/A 18576-2026 artfynd.xlsx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor/A 18576-2026 karta.png", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/kartor_geotiff/A 18576-2026 georefererad karta.tif", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomål/A 18576-2026 FSC-klagomål.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/klagomålsmail/A 18576-2026 FSC-klagomål mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsyn/A 18576-2026 tillsynsbegäran.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0330/tillsynsmail/A 18576-2026 tillsynsbegäran mail.docx", "A 18576-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 61768-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46304</v>
+      </c>
+ 